--- a/Assets/Internationalization/Tutorial_String_Data.xlsx
+++ b/Assets/Internationalization/Tutorial_String_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Game Projects\Godot Projects\city_of_circling\Assets\Internationalization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F1CE0AC-E27B-42BF-9A6F-70E4B0A0A407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97C390E5-7990-467D-A2B1-0579AA4016E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{08590711-CB36-410F-B5A8-7B8F5AA8D814}"/>
+    <workbookView xWindow="3510" yWindow="615" windowWidth="31800" windowHeight="20985" xr2:uid="{08590711-CB36-410F-B5A8-7B8F5AA8D814}"/>
   </bookViews>
   <sheets>
     <sheet name="String_Data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
   <si>
     <t>en</t>
   </si>
@@ -92,9 +92,6 @@
   </si>
   <si>
     <t>TUTORIAL_UPGRADE_2</t>
-  </si>
-  <si>
-    <t>“感谢你的水果！送你 2 张交换券，可以在商店买东西用哦。”</t>
   </si>
   <si>
     <t>TUTORIAL_GATE_BUTTON</t>
@@ -143,50 +140,24 @@
     <t>“我想要 1 个苹果和 1 串葡萄，拜托了！”</t>
   </si>
   <si>
-    <t>TUTORIAL_NPC_11</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>另一位城民似乎也有请求？拜访看看吧。</t>
-  </si>
-  <si>
-    <t>TUTORIAL_NPC_12</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>获得了 1 个苹果。\n虽然不知道能用来做什么...</t>
   </si>
   <si>
     <t>前面的格子或许可以抽到。\n试试看吧。</t>
   </si>
   <si>
-    <t>欢迎来到盘旋城。</t>
-  </si>
-  <si>
     <t>点一下角色就能开始移动。</t>
   </si>
   <si>
     <t>移动鼠标沿格子规划路径，点一下终点就能确认。</t>
   </si>
   <si>
-    <t>移动一次会消耗 1 小时，要留意哦。</t>
-  </si>
-  <si>
     <t>试着走到那个奇怪的格子上吧。</t>
   </si>
   <si>
-    <t>一位城民似乎需要帮助。\n拜访看看吧。</t>
-  </si>
-  <si>
     <t>还差 1 串葡萄，就能完成委托。</t>
   </si>
   <si>
-    <t>抽到了需要的水果。\n现在回去交给城民吧。</t>
-  </si>
-  <si>
-    <t>另外，不同于接受水果委托，\n提交水果不用停下脚步，路过城民时就会自动交付。</t>
-  </si>
-  <si>
     <t>传信任务路过目标也能自动完成。\n好好利用可以节省时间哦。</t>
   </si>
   <si>
@@ -199,36 +170,12 @@
     <t>获得了 2 个自选水果。\n点击亮着的水果图标，挑你想要的吧。</t>
   </si>
   <si>
-    <t>升级商店里，可以用升级券解锁各种能力。</t>
-  </si>
-  <si>
     <t>现在还没有升级券呢。\n先努力完成委托，在商店里买 1 张吧。</t>
   </si>
   <si>
-    <t>获得了 1 张贸易升级券。\n去贸易升级商店看看吧。</t>
-  </si>
-  <si>
-    <t>目前这里有两种升级可选。\n先买“商店刷新+”吧。</t>
-  </si>
-  <si>
-    <t>升级商店通常会卖 基础升级 和 特殊升级。</t>
-  </si>
-  <si>
     <t>基础升级可以反复购买，等级和效果随之提升。\n可以在描述中查看当前等级和效果。</t>
   </si>
   <si>
-    <t>刚刚买到的是 “商店刷新+”，现在可以手动刷新商店。</t>
-  </si>
-  <si>
-    <t>除了无限供应的 3%s 盲盒，其他商品买完都会暂时缺货。</t>
-  </si>
-  <si>
-    <t>商店会在每天 00:00 / 08:00 / 16:00 上架随机商品，或者手动刷新时也会更新。</t>
-  </si>
-  <si>
-    <t>手动刷新次数会在每日00:00重置。</t>
-  </si>
-  <si>
     <t>准备妥当的话，就前往城门结束教程，正式开始游戏吧。</t>
   </si>
   <si>
@@ -266,100 +213,224 @@
   </si>
   <si>
     <t>Things are a bit pricey right now.\nHow about trying a Mystery Box?</t>
-  </si>
-  <si>
-    <t>There are two upgrades available here.\nGet "Shop Refresh+" first.</t>
-  </si>
-  <si>
-    <t>You just got "Shop Refresh+", so now you can manually refresh the shop.</t>
-  </si>
-  <si>
-    <t>Except for the unlimited 3%s Mystery Boxes, other items go out of stock after purchase.</t>
-  </si>
-  <si>
-    <t>Manual refresh uses reset daily at 00:00.</t>
-  </si>
-  <si>
-    <t>When you're ready, head to the city gate to end the tutorial and start the real game!</t>
   </si>
   <si>
     <t>You're ready to proceed.</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Welcome to the City of Circling.</t>
+    <t>Welcome to the City of Stayvesant to prepare for the upcoming adventure.</t>
+  </si>
+  <si>
+    <t>欢迎来到斗鎏城，为即将到来的冒险做准备。</t>
+  </si>
+  <si>
+    <t>Move your mouse along tiles to plan a path, \nthen click the destination to confirm.</t>
+  </si>
+  <si>
+    <t>Each move takes 3 hour. Keep that in mind.</t>
+  </si>
+  <si>
+    <t>移动一次会消耗 3 小时，要留意哦。</t>
+  </si>
+  <si>
+    <t>add_grid()</t>
+  </si>
+  <si>
+    <t>Someone seems to need help.\nGo pay them a visit.</t>
+  </si>
+  <si>
+    <t>似乎有人需要帮助。\n拜访看看吧。</t>
+  </si>
+  <si>
+    <t>抽到了需要的水果。\n现在回去交给ta吧。</t>
+  </si>
+  <si>
+    <t>"Thanks for the fruit! Here's 2 Exchange Coupons you can use at the shop."</t>
+  </si>
+  <si>
+    <t>“感谢你的水果！送你 2 张交换券，可以在商店买冒险物资用哦。”</t>
+  </si>
+  <si>
+    <t>另外，不同于接受水果委托，\n提交水果不用停留，路过时就会自动交付。</t>
+  </si>
+  <si>
+    <t>除了水果，有时也会接到传信的委托。</t>
+  </si>
+  <si>
+    <t>Another request? Go check it out.</t>
+  </si>
+  <si>
+    <t>另一位似乎也有请求？拜访看看吧。</t>
+  </si>
+  <si>
+    <t>"可以麻烦帮我捎个口信给长颈鹿吗？拜托了！”</t>
+  </si>
+  <si>
+    <t>"Thanks for the message! Here's 1 Exchange Coupon. Check out the shop nearby when you can."</t>
+  </si>
+  <si>
+    <t>“感谢稍信！给你 1 张交换券，有空的话去附近的商店看看吧。”</t>
+  </si>
+  <si>
+    <t>TUTORIAL_NPC_11</t>
+  </si>
+  <si>
+    <t>Besides fruit requests, you'll sometimes get message delivery requests.</t>
+  </si>
+  <si>
+    <t>TUTORIAL_NPC_12</t>
+  </si>
+  <si>
+    <t>The shop is open! You can buy things with Exchange Coupons.\nTake a look.</t>
+  </si>
+  <si>
+    <t>You got 2 Fruits of your choice!\nClick the glowing fruit icons to pick the ones you want.</t>
+  </si>
+  <si>
+    <t>The Upgrade Tiles let you unlock abilities with Upgrade Coupons.</t>
+  </si>
+  <si>
+    <t>在升级格可以用升级券解锁各种能力。</t>
+  </si>
+  <si>
+    <t>You don't have any Upgrade Coupons yet.\nComplete some requests first, then buy one at the shop.</t>
+  </si>
+  <si>
+    <t>You got 1 Trade Upgrade Coupon!\nVisit the Shop Upgrade Grid.</t>
+  </si>
+  <si>
+    <t>There are two upgrades available here.\nGet "Shop Manual Refresh" first.</t>
+  </si>
+  <si>
+    <t>目前这里有两种升级可选。\n先买“解锁商店刷新”吧。</t>
+  </si>
+  <si>
+    <t>Upgrade Tiles usually sell both Basic Upgrades and Special Upgrades.</t>
+  </si>
+  <si>
+    <t>升级格通常会同时卖 基础升级 和 特殊升级。</t>
+  </si>
+  <si>
+    <t>Basic Upgrades can be bought multiple times, improving with each level.\nCheck the tooltip for current level and effects.</t>
+  </si>
+  <si>
+    <t>You just got "Shop Manual Refresh", so now you can manually refresh the shop.</t>
+  </si>
+  <si>
+    <t>刚刚买到的是 “解锁商店刷新”，现在可以手动刷新商店。</t>
+  </si>
+  <si>
+    <t>Except for the unlimited Mystery Boxes, other items go out of stock after purchase.</t>
+  </si>
+  <si>
+    <t>除了无限供应的盲盒，其他商品买完都会暂时缺货。</t>
+  </si>
+  <si>
+    <t>The shop restocks at 00:00 daily with random goods, or when you manually refresh.</t>
+  </si>
+  <si>
+    <t>商店会在每天 00:00上架随机商品，或者手动刷新时也会更新。</t>
+  </si>
+  <si>
+    <t>Manual refresh refills to 3 uses daily at 00:00.</t>
+  </si>
+  <si>
+    <t>手动刷新次数会在每日00:00重置为 3 次。</t>
+  </si>
+  <si>
+    <t>TUTORIAL_UPGRADE_11</t>
+  </si>
+  <si>
+    <t>Please visit the shop again and buy the Shopping Cart.\nIf it isn’t available, try the manual refresh you just unlocked,\nor wait for a restock.</t>
+  </si>
+  <si>
+    <t>请再次拜访商店，买下 购物车 吧。\n如果目前没有上架的话，试试刚解锁的手动刷新，\n或者打发一会儿时间吧。</t>
+  </si>
+  <si>
+    <t>TUTORIAL_POINTS_1</t>
+  </si>
+  <si>
+    <t>The Shopping Cart is a rare item,\nand provides 5 Shop Pts.</t>
+  </si>
+  <si>
+    <t>买到的 购物车 稀有度较高，可以提供 5 点商店点数。</t>
+  </si>
+  <si>
+    <t>TUTORIAL_POINTS_2</t>
+  </si>
+  <si>
+    <t>Raising different types of points increases adventure success rate.\nBut only when LUCK, MOVEMENT, QUEST, and SHOP Pts all work together\nthe effect will be significant.</t>
+  </si>
+  <si>
+    <t>TUTORIAL_POINTS_3</t>
+  </si>
+  <si>
+    <t>LUCK, MOVEMENT, and QUEST items are sold at their respective shops.\nThey’re not available yet, so let’s give you some for demonstration.</t>
+  </si>
+  <si>
+    <t>幸运、移动、任务物资在对应的商店出售。\n目前没有地方能买到呢，先发放一些物资以作说明吧。</t>
+  </si>
+  <si>
+    <t>TUTORIAL_POINTS_4</t>
+  </si>
+  <si>
+    <t>Success rate increased!\nThe more items you prepare, the less likely you are to fail.\nIf you fail... you’ll return empty-handed.</t>
+  </si>
+  <si>
+    <t>冒险成功率提升了！\n物资准备越充分，就越能够避免冒险失败的情况。\n如果失败的话...就一无所获了呢。</t>
+  </si>
+  <si>
+    <t>TUTORIAL_POINTS_5</t>
+  </si>
+  <si>
+    <t>You have 60 days in total.\nThe more time you spend stocking up in the city, the less time you’ll have to venture out.\nAdventure scores also decrease as days pass. Keep that in mind.</t>
+  </si>
+  <si>
+    <t>此外，一共有 60 天的时间。\n花费更多时间在城里囤积物资的话，可用于出城冒险的时间则会相应减少。\n能够获得的冒险得分也会随天数降低。请注意。</t>
+  </si>
+  <si>
+    <t>TUTORIAL_POINTS_6</t>
+  </si>
+  <si>
+    <t>The goal is to achieve a higher adventure score.\nSo, improve your efficiency in stocking up.\nRaise your Success Rate while saving more days for the adventure itself!</t>
+  </si>
+  <si>
+    <t>游戏的目标是获取更高的冒险得分。\n因此，提高在城里准备物资的效率。\n在提高冒险成功率的同时，努力留出更多天数用来冒险吧。</t>
+  </si>
+  <si>
+    <t>When you're ready, head to the city gate to end the tutorial and start the game!</t>
+  </si>
+  <si>
+    <t>提升各类点数可以增加冒险成功率。\n不过需要幸运、移动、任务、商店四项点数共同作用，效果才会显著哦。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Move your mouse along tiles to plan a path, \nthen click the destination to confirm.</t>
+    <t>获得了 1 张商店升级券。\n去商店升级格看看吧。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Each move takes 1 hour. Keep that in mind.</t>
+    <t>SKIP_TUTORIAL</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>A citizen seems to need help.\nGo pay them a visit.</t>
+    <t>跳过教程</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Another citizen has a request too? Go check it out.</t>
+    <t>Skip Tutorial</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>"Thanks for the fruit! Here's 2 Exchange Coupons you can use at the shop."</t>
+    <t>SKIP_TUTORIAL_CONFIRM</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>"Thanks for the message! Here's 1 Exchange Coupon. Check out the shop nearby when you can."</t>
+    <t>Are you sure to skip tutorial?</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Besides fruit requests, you'll sometimes get message delivery requests.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>The shop is open! You can buy things with Exchange Coupons.\nTake a look.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>You got 2 Fruits of your choice!\nClick the glowing fruit icons to pick the ones you want.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>The Upgrade Shop lets you unlock abilities with Upgrade Coupons.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>You don't have any Upgrade Coupons yet.\nComplete some requests first, then buy one at the shop.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>You got 1 Trade Upgrade Coupon!\nVisit the Trade Upgrade Shop.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Upgrade Shops usually sell Basic Upgrades and Special Upgrades.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Basic Upgrades can be bought multiple times, improving with each level.\nCheck the tooltip for current level and effects.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>The shop restocks at 00:00 / 08:00 / 16:00 daily with random goods, or when you manually refresh.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>除了水果，有时也会接到传信的委托。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>"可以麻烦帮我传个口信给长颈鹿吗？拜托了！”</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>“感谢传信！给你 1 张交换券，有空的话去附近的商店看看吧。”</t>
+    <t>确定要跳过教程吗？</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1333,7 +1404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2D1D195-E5E8-4810-8E47-E25327235024}">
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="36.75" customWidth="1"/>
@@ -1354,103 +1425,120 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
+      <c r="A4" t="s">
+        <v>127</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>44</v>
+        <v>129</v>
+      </c>
+      <c r="C4" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
+      <c r="A5" t="s">
+        <v>130</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>45</v>
+        <v>131</v>
+      </c>
+      <c r="C5" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>87</v>
+        <v>3</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>88</v>
+        <v>4</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="2"/>
-      <c r="C8" s="2"/>
+      <c r="A8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>70</v>
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="2"/>
-      <c r="C11" s="2"/>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="2"/>
-      <c r="C12" s="2"/>
+      <c r="B12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2"/>
@@ -1461,48 +1549,41 @@
       <c r="C14" s="2"/>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>49</v>
-      </c>
+      <c r="A15" s="2"/>
+      <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>38</v>
-      </c>
+      <c r="A16" s="2"/>
+      <c r="C16" s="2"/>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="2"/>
-      <c r="C18" s="2"/>
+      <c r="A18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>43</v>
@@ -1514,272 +1595,360 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" t="s">
-        <v>75</v>
+        <v>12</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="A22" s="2"/>
+      <c r="C22" s="2"/>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B23" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="2"/>
-      <c r="C24" s="2"/>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="2"/>
-      <c r="C25" s="2"/>
+      <c r="B25" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2"/>
       <c r="C26" s="2"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B27" t="s">
-        <v>90</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>40</v>
-      </c>
+      <c r="A27" s="2"/>
+      <c r="C27" s="2"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B28" t="s">
-        <v>77</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>103</v>
-      </c>
+      <c r="A28" s="2"/>
+      <c r="C28" s="2"/>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="2"/>
-      <c r="C32" s="2"/>
+      <c r="A32" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B32" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B34" t="s">
-        <v>79</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>55</v>
-      </c>
+      <c r="A34" s="2"/>
+      <c r="C34" s="2"/>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B35" t="s">
-        <v>95</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="2"/>
-      <c r="C36" s="2"/>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="2"/>
-      <c r="C37" s="2"/>
+      <c r="B37" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B38" t="s">
-        <v>96</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="A38" s="2"/>
+      <c r="C38" s="2"/>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B39" t="s">
-        <v>97</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>58</v>
-      </c>
+      <c r="A39" s="2"/>
+      <c r="C39" s="2"/>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B40" t="s">
-        <v>98</v>
+        <v>22</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B41" t="s">
-        <v>80</v>
+        <v>23</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B42" t="s">
-        <v>99</v>
+        <v>27</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="14.25" customHeight="1">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B43" t="s">
-        <v>100</v>
+        <v>28</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="14.25" customHeight="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B44" t="s">
-        <v>81</v>
+        <v>29</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="14.25" customHeight="1">
       <c r="A45" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A46" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A47" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B45" t="s">
-        <v>82</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B46" t="s">
+      <c r="B48" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B47" t="s">
-        <v>83</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="2"/>
-      <c r="C48" s="2"/>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B49" t="s">
-        <v>84</v>
+        <v>34</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>67</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="28.5">
+      <c r="A50" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="28.5">
+      <c r="A52" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="28.5">
+      <c r="A53" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="28.5">
+      <c r="A54" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="28.5">
+      <c r="A55" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="28.5">
+      <c r="A56" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Internationalization/Tutorial_String_Data.xlsx
+++ b/Assets/Internationalization/Tutorial_String_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Game Projects\Godot Projects\city_of_circling\Assets\Internationalization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97C390E5-7990-467D-A2B1-0579AA4016E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75061183-5F41-4C2F-977D-186CD66C9224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3510" yWindow="615" windowWidth="31800" windowHeight="20985" xr2:uid="{08590711-CB36-410F-B5A8-7B8F5AA8D814}"/>
   </bookViews>
@@ -167,9 +167,6 @@
     <t>现在商品有点贵。\n不如先买个盲盒碰碰运气？</t>
   </si>
   <si>
-    <t>获得了 2 个自选水果。\n点击亮着的水果图标，挑你想要的吧。</t>
-  </si>
-  <si>
     <t>现在还没有升级券呢。\n先努力完成委托，在商店里买 1 张吧。</t>
   </si>
   <si>
@@ -431,6 +428,10 @@
   </si>
   <si>
     <t>确定要跳过教程吗？</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得了 2 个自选水果。\n点击亮着的水果图标，挑选想要的吧。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1428,7 +1429,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
         <v>26</v>
@@ -1439,7 +1440,7 @@
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
         <v>36</v>
@@ -1447,24 +1448,24 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C4" t="s">
         <v>127</v>
-      </c>
-      <c r="B4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C4" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" t="s">
         <v>130</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>131</v>
-      </c>
-      <c r="C5" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1472,10 +1473,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1483,7 +1484,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>40</v>
@@ -1494,7 +1495,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>41</v>
@@ -1505,15 +1506,15 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -1523,7 +1524,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>42</v>
@@ -1534,7 +1535,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>38</v>
@@ -1561,10 +1562,10 @@
         <v>9</v>
       </c>
       <c r="B17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1572,7 +1573,7 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>37</v>
@@ -1583,7 +1584,7 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>43</v>
@@ -1598,7 +1599,7 @@
         <v>12</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>39</v>
@@ -1613,10 +1614,10 @@
         <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1624,10 +1625,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1635,10 +1636,10 @@
         <v>15</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1658,10 +1659,10 @@
         <v>16</v>
       </c>
       <c r="B29" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1669,10 +1670,10 @@
         <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1680,29 +1681,29 @@
         <v>18</v>
       </c>
       <c r="B31" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B32" t="s">
         <v>82</v>
       </c>
-      <c r="B32" t="s">
-        <v>83</v>
-      </c>
       <c r="C32" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>44</v>
@@ -1717,7 +1718,7 @@
         <v>19</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>45</v>
@@ -1728,7 +1729,7 @@
         <v>20</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>46</v>
@@ -1739,10 +1740,10 @@
         <v>21</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>47</v>
+        <v>132</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1758,10 +1759,10 @@
         <v>22</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1769,10 +1770,10 @@
         <v>23</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1780,10 +1781,10 @@
         <v>27</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1791,10 +1792,10 @@
         <v>28</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1802,10 +1803,10 @@
         <v>29</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="14.25" customHeight="1">
@@ -1813,10 +1814,10 @@
         <v>30</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="14.25" customHeight="1">
@@ -1824,10 +1825,10 @@
         <v>31</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="14.25" customHeight="1">
@@ -1835,10 +1836,10 @@
         <v>32</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1846,10 +1847,10 @@
         <v>33</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1857,87 +1858,87 @@
         <v>34</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="28.5">
       <c r="A50" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="C50" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="C51" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="28.5">
       <c r="A52" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="C52" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="28.5">
       <c r="A53" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="C53" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="28.5">
       <c r="A54" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="C54" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="28.5">
       <c r="A55" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="C55" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="28.5">
       <c r="A56" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="C56" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1945,10 +1946,10 @@
         <v>35</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Internationalization/Tutorial_String_Data.xlsx
+++ b/Assets/Internationalization/Tutorial_String_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Game Projects\Godot Projects\city_of_circling\Assets\Internationalization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75061183-5F41-4C2F-977D-186CD66C9224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EBD6534-A3FC-469F-869E-DEF132C050D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3510" yWindow="615" windowWidth="31800" windowHeight="20985" xr2:uid="{08590711-CB36-410F-B5A8-7B8F5AA8D814}"/>
   </bookViews>
@@ -333,25 +333,10 @@
     <t>Manual refresh refills to 3 uses daily at 00:00.</t>
   </si>
   <si>
-    <t>手动刷新次数会在每日00:00重置为 3 次。</t>
-  </si>
-  <si>
     <t>TUTORIAL_UPGRADE_11</t>
   </si>
   <si>
-    <t>Please visit the shop again and buy the Shopping Cart.\nIf it isn’t available, try the manual refresh you just unlocked,\nor wait for a restock.</t>
-  </si>
-  <si>
-    <t>请再次拜访商店，买下 购物车 吧。\n如果目前没有上架的话，试试刚解锁的手动刷新，\n或者打发一会儿时间吧。</t>
-  </si>
-  <si>
     <t>TUTORIAL_POINTS_1</t>
-  </si>
-  <si>
-    <t>The Shopping Cart is a rare item,\nand provides 5 Shop Pts.</t>
-  </si>
-  <si>
-    <t>买到的 购物车 稀有度较高，可以提供 5 点商店点数。</t>
   </si>
   <si>
     <t>TUTORIAL_POINTS_2</t>
@@ -433,6 +418,22 @@
   <si>
     <t>获得了 2 个自选水果。\n点击亮着的水果图标，挑选想要的吧。</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>手动刷新次数会在每日00:00重置为 3 次。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Please visit the shop again and buy the [font_size=40][color=#94b757]Balance[/color][/font_size].\nIf it isn’t available, try the manual refresh you just unlocked.</t>
+  </si>
+  <si>
+    <t>请再次拜访商店，买下 [font_size=40][color=#94b757]天平[/color][/font_size] 吧。\n如果目前没有上架的话，试试刚解锁的手动刷新吧。</t>
+  </si>
+  <si>
+    <t>The [font_size=40][color=#94b757]天平[/color][/font_size] provides 5 Shop Pts.</t>
+  </si>
+  <si>
+    <t>买到的 [font_size=40][color=#94b757]天平[/color][/font_size] 可以提供 3 点商店点数。</t>
   </si>
 </sst>
 </file>
@@ -1448,24 +1449,24 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B5" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1743,7 +1744,7 @@
         <v>85</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1784,7 +1785,7 @@
         <v>89</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1861,84 +1862,84 @@
         <v>101</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="28.5">
       <c r="A50" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="28.5">
       <c r="A52" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="28.5">
       <c r="A53" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="28.5">
       <c r="A54" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="28.5">
       <c r="A55" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="28.5">
       <c r="A56" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1946,7 +1947,7 @@
         <v>35</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>49</v>

--- a/Assets/Internationalization/Tutorial_String_Data.xlsx
+++ b/Assets/Internationalization/Tutorial_String_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Game Projects\Godot Projects\city_of_circling\Assets\Internationalization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EBD6534-A3FC-469F-869E-DEF132C050D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E987EC52-A35E-4892-AAC3-2A14A964DFFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="615" windowWidth="31800" windowHeight="20985" xr2:uid="{08590711-CB36-410F-B5A8-7B8F5AA8D814}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{08590711-CB36-410F-B5A8-7B8F5AA8D814}"/>
   </bookViews>
   <sheets>
     <sheet name="String_Data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
   <si>
     <t>en</t>
   </si>
@@ -121,15 +121,6 @@
     <t>TUTORIAL_UPGRADE_7</t>
   </si>
   <si>
-    <t>TUTORIAL_UPGRADE_8</t>
-  </si>
-  <si>
-    <t>TUTORIAL_UPGRADE_9</t>
-  </si>
-  <si>
-    <t>TUTORIAL_UPGRADE_10</t>
-  </si>
-  <si>
     <t>TUTORIAL_GATE</t>
   </si>
   <si>
@@ -137,310 +128,621 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>“我想要 1 个苹果和 1 串葡萄，拜托了！”</t>
-  </si>
-  <si>
-    <t>获得了 1 个苹果。\n虽然不知道能用来做什么...</t>
-  </si>
-  <si>
     <t>前面的格子或许可以抽到。\n试试看吧。</t>
   </si>
   <si>
-    <t>点一下角色就能开始移动。</t>
-  </si>
-  <si>
-    <t>移动鼠标沿格子规划路径，点一下终点就能确认。</t>
-  </si>
-  <si>
-    <t>试着走到那个奇怪的格子上吧。</t>
-  </si>
-  <si>
-    <t>还差 1 串葡萄，就能完成委托。</t>
-  </si>
-  <si>
-    <t>传信任务路过目标也能自动完成。\n好好利用可以节省时间哦。</t>
-  </si>
-  <si>
-    <t>商店开张了，可以用交换券买东西。\n进去看看吧。</t>
-  </si>
-  <si>
-    <t>现在商品有点贵。\n不如先买个盲盒碰碰运气？</t>
-  </si>
-  <si>
-    <t>现在还没有升级券呢。\n先努力完成委托，在商店里买 1 张吧。</t>
-  </si>
-  <si>
-    <t>基础升级可以反复购买，等级和效果随之提升。\n可以在描述中查看当前等级和效果。</t>
+    <t>End Tutorial</t>
+  </si>
+  <si>
+    <t>Click on your character to start moving.</t>
+  </si>
+  <si>
+    <t>That tile ahead might have some.\nGive it a try.</t>
+  </si>
+  <si>
+    <t>Got the fruit you needed!\nNow head back to deliver it.</t>
+  </si>
+  <si>
+    <t>add_grid()</t>
+  </si>
+  <si>
+    <t>Someone seems to need help.\nGo pay them a visit.</t>
+  </si>
+  <si>
+    <t>TUTORIAL_NPC_11</t>
+  </si>
+  <si>
+    <t>The shop is open! You can buy things with Exchange Coupons.\nTake a look.</t>
+  </si>
+  <si>
+    <t>TUTORIAL_POINTS_1</t>
+  </si>
+  <si>
+    <t>TUTORIAL_POINTS_2</t>
+  </si>
+  <si>
+    <t>TUTORIAL_POINTS_3</t>
+  </si>
+  <si>
+    <t>TUTORIAL_POINTS_4</t>
+  </si>
+  <si>
+    <t>TUTORIAL_POINTS_5</t>
+  </si>
+  <si>
+    <t>TUTORIAL_POINTS_6</t>
+  </si>
+  <si>
+    <t>SKIP_TUTORIAL</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>跳过教程</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKIP_TUTORIAL_CONFIRM</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>确定要跳过教程吗？</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TUTORIAL_2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>欢迎来到教程。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>为了应对即将到来的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>冒险，\n 现在开始在城里进行准备吧</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击角色开始移动。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>沿着格子移动鼠标来规划路径，在终点点击进行确认。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>每次移动会消耗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[color=#BC3D37]</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3小时[/color]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，还请留意。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>试着移动到那个奇怪的格子上吧。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得了[font_size=40] 苹果 x 1[/font_size]。\n虽然不知道能用来做什么...</t>
+  </si>
+  <si>
+    <t>似乎有人需要帮助。\n去拜访看看吧。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>还差[font_size=40] 葡萄 x 1[/font_size] 就能完成委托。</t>
+  </si>
+  <si>
+    <t>抽到了需要的水果。\n现在回去提交吧。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>“我需要[font_size=40] 苹果 x 1[/font_size] 和[font_size=40] 葡萄 x 1[/font_size]，拜托了！”</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>不同于[font_size=40] 接受任务[/font_size]，\n</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[font_size=40]完成</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>任务</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> [/font_size]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>时不需要停留在格子上，路过就会自动交付。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>“感谢你的水果！送你[font_size=40] 交换券 x 2[/font_size]，可以用来在商店购物哦。”</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>另一位似乎也有[font_size=40] 任务[/font_size]？拜访看看吧。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>"可以麻烦帮我传个信给长颈鹿吗？拜托了！”</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>除了水果，有时也会接到传信的[font_size=40] 任务[/font_size]。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>“感谢！给你[font_size=40] 交换券 x 1[/font_size]，有空的话去附近的商店看看吧。”</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>商店开张，可以用交换券购物了。\n进去看看吧。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他商品有点贵。\n不如先买个盲盒碰碰运气？</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得了[font_size=40] 自选水果 x 2[/font_size]。\n点击闪烁的水果图标，挑选想要的吧。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>除了无限供应的盲盒，其他商品出售后都会暂时缺货。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前有两种升级可选。\n不如先买“解锁商店刷新”？</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>有些升级项可以反复购买，等级和效果随之提升。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>商店会在</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[color=#BC3D37]每天 00:00 [/color]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>上架随机商品，同时重置3次手动刷新次数。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>在</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[font_size=40] 升级格 [/font_size]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>可以用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">[font_size=40] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>升级券</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> [/font_size]购买各种</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[font_size=40] 升级[/font_size]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得了[font_size=40] 商店升级券 x 1[/font_size]。\n去商店升级格看看吧。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在请从商店获取[font_size=40][color=#94b757] 天平 [/color] x 1 [/font_size]吧。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升各类点数可以增加冒险成功率。\n不过需要四种点数共同作用，效果才会显著哦。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>四类点数道具会在对应的商店出售。\n目前没有商店能买到其他三类呢，先发放一些道具以作说明吧。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>冒险成功率提升了！\n道具准备越充分，就越能够避免冒险失败的情况。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TUTORIAL_POINTS_7</t>
+  </si>
+  <si>
+    <t>TUTORIAL_POINTS_8</t>
+  </si>
+  <si>
+    <t>TUTORIAL_POINTS_9</t>
+  </si>
+  <si>
+    <r>
+      <t>如果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[font_size=40] 失败 [/font_size]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的话...就[color=#BC3D37] 一无所获 [/color]了呢。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>此外，游戏一共有[color=#BC3D37] 60 天[/color]的时间。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>花费更多时间在城里囤积道具的话，可用于出城冒险的时间则会相应减少。\n能够获得的[color=#BC3D37]  冒险得分 [/color]也会随天数降低。请注意。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏的目标是获取更高的[color=#BC3D37]  冒险得分[/color]。\n因此, 在城里囤积道具的同时，努力留出更多时间用来冒险吧。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>You're ready to proceed.</t>
+  </si>
+  <si>
+    <t>Skip Tutorial</t>
+  </si>
+  <si>
+    <t>Welcome to the Tutorial.</t>
+  </si>
+  <si>
+    <t>Move your mouse along the tiles to plan a path,\nthen click the destination to confirm.</t>
+  </si>
+  <si>
+    <t>Are you sure to skip the tutorial?</t>
+  </si>
+  <si>
+    <t>Each move takes [color=#BC3D37]3 hours[/color]. Keep that in mind.</t>
+  </si>
+  <si>
+    <t>“Could you deliver a message to the Giraffe for me? Please!”</t>
+  </si>
+  <si>
+    <t>Other items are a bit pricey for now.\nHow about trying a Mystery Box instead?</t>
+  </si>
+  <si>
+    <t>Adventure success rate increased!\nThe more items you prepare, the less likely you are to fail.</t>
+  </si>
+  <si>
+    <t>Spending more time stocking up in the city means less time left for adventures.\nYour [color=#BC3D37]Adventure Score[/color] will also decrease as days pass. Keep that in mind.</t>
+  </si>
+  <si>
+    <t>The goal is to achieve a higher [color=#BC3D37]Adventure Score[/color].\nSo, stock up efficiently and leave more time for the adventure itself!</t>
+  </si>
+  <si>
+    <t>The game lasts [color=#BC3D37]60 days[/color] in total.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>准备妥当的话，就前往城门结束教程，正式开始游戏吧。</t>
-  </si>
-  <si>
-    <t>End Tutorial</t>
-  </si>
-  <si>
-    <t>Click on your character to start moving.</t>
-  </si>
-  <si>
-    <t>Try stepping on that strange tile over there.</t>
-  </si>
-  <si>
-    <t>You got 1 Apple!\nNot sure what it's for yet...</t>
-  </si>
-  <si>
-    <t>"I need 1 Apple and 1 Grapes, please!"</t>
-  </si>
-  <si>
-    <t>Just 1 Grapes left to complete the request.</t>
-  </si>
-  <si>
-    <t>That tile ahead might have some.\nGive it a try.</t>
-  </si>
-  <si>
-    <t>Got the fruit you needed!\nNow head back to deliver it.</t>
-  </si>
-  <si>
-    <t>By the way, unlike accepting requests,\nyou can deliver fruit just by passing by. No need to stop!</t>
-  </si>
-  <si>
-    <t>"Could you deliver a message to the Giraffe for me? Please!"</t>
-  </si>
-  <si>
-    <t>Message deliveries complete automatically when you pass by too.\nUse this to save time!</t>
-  </si>
-  <si>
-    <t>Things are a bit pricey right now.\nHow about trying a Mystery Box?</t>
-  </si>
-  <si>
-    <t>You're ready to proceed.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Welcome to the City of Stayvesant to prepare for the upcoming adventure.</t>
-  </si>
-  <si>
-    <t>欢迎来到斗鎏城，为即将到来的冒险做准备。</t>
-  </si>
-  <si>
-    <t>Move your mouse along tiles to plan a path, \nthen click the destination to confirm.</t>
-  </si>
-  <si>
-    <t>Each move takes 3 hour. Keep that in mind.</t>
-  </si>
-  <si>
-    <t>移动一次会消耗 3 小时，要留意哦。</t>
-  </si>
-  <si>
-    <t>add_grid()</t>
-  </si>
-  <si>
-    <t>Someone seems to need help.\nGo pay them a visit.</t>
-  </si>
-  <si>
-    <t>似乎有人需要帮助。\n拜访看看吧。</t>
-  </si>
-  <si>
-    <t>抽到了需要的水果。\n现在回去交给ta吧。</t>
-  </si>
-  <si>
-    <t>"Thanks for the fruit! Here's 2 Exchange Coupons you can use at the shop."</t>
-  </si>
-  <si>
-    <t>“感谢你的水果！送你 2 张交换券，可以在商店买冒险物资用哦。”</t>
-  </si>
-  <si>
-    <t>另外，不同于接受水果委托，\n提交水果不用停留，路过时就会自动交付。</t>
-  </si>
-  <si>
-    <t>除了水果，有时也会接到传信的委托。</t>
-  </si>
-  <si>
-    <t>Another request? Go check it out.</t>
-  </si>
-  <si>
-    <t>另一位似乎也有请求？拜访看看吧。</t>
-  </si>
-  <si>
-    <t>"可以麻烦帮我捎个口信给长颈鹿吗？拜托了！”</t>
-  </si>
-  <si>
-    <t>"Thanks for the message! Here's 1 Exchange Coupon. Check out the shop nearby when you can."</t>
-  </si>
-  <si>
-    <t>“感谢稍信！给你 1 张交换券，有空的话去附近的商店看看吧。”</t>
-  </si>
-  <si>
-    <t>TUTORIAL_NPC_11</t>
-  </si>
-  <si>
-    <t>Besides fruit requests, you'll sometimes get message delivery requests.</t>
-  </si>
-  <si>
-    <t>TUTORIAL_NPC_12</t>
-  </si>
-  <si>
-    <t>The shop is open! You can buy things with Exchange Coupons.\nTake a look.</t>
-  </si>
-  <si>
-    <t>You got 2 Fruits of your choice!\nClick the glowing fruit icons to pick the ones you want.</t>
-  </si>
-  <si>
-    <t>The Upgrade Tiles let you unlock abilities with Upgrade Coupons.</t>
-  </si>
-  <si>
-    <t>在升级格可以用升级券解锁各种能力。</t>
-  </si>
-  <si>
-    <t>You don't have any Upgrade Coupons yet.\nComplete some requests first, then buy one at the shop.</t>
-  </si>
-  <si>
-    <t>You got 1 Trade Upgrade Coupon!\nVisit the Shop Upgrade Grid.</t>
-  </si>
-  <si>
-    <t>There are two upgrades available here.\nGet "Shop Manual Refresh" first.</t>
-  </si>
-  <si>
-    <t>目前这里有两种升级可选。\n先买“解锁商店刷新”吧。</t>
-  </si>
-  <si>
-    <t>Upgrade Tiles usually sell both Basic Upgrades and Special Upgrades.</t>
-  </si>
-  <si>
-    <t>升级格通常会同时卖 基础升级 和 特殊升级。</t>
-  </si>
-  <si>
-    <t>Basic Upgrades can be bought multiple times, improving with each level.\nCheck the tooltip for current level and effects.</t>
-  </si>
-  <si>
-    <t>You just got "Shop Manual Refresh", so now you can manually refresh the shop.</t>
-  </si>
-  <si>
-    <t>刚刚买到的是 “解锁商店刷新”，现在可以手动刷新商店。</t>
-  </si>
-  <si>
-    <t>Except for the unlimited Mystery Boxes, other items go out of stock after purchase.</t>
-  </si>
-  <si>
-    <t>除了无限供应的盲盒，其他商品买完都会暂时缺货。</t>
-  </si>
-  <si>
-    <t>The shop restocks at 00:00 daily with random goods, or when you manually refresh.</t>
-  </si>
-  <si>
-    <t>商店会在每天 00:00上架随机商品，或者手动刷新时也会更新。</t>
-  </si>
-  <si>
-    <t>Manual refresh refills to 3 uses daily at 00:00.</t>
-  </si>
-  <si>
-    <t>TUTORIAL_UPGRADE_11</t>
-  </si>
-  <si>
-    <t>TUTORIAL_POINTS_1</t>
-  </si>
-  <si>
-    <t>TUTORIAL_POINTS_2</t>
-  </si>
-  <si>
-    <t>Raising different types of points increases adventure success rate.\nBut only when LUCK, MOVEMENT, QUEST, and SHOP Pts all work together\nthe effect will be significant.</t>
-  </si>
-  <si>
-    <t>TUTORIAL_POINTS_3</t>
-  </si>
-  <si>
-    <t>LUCK, MOVEMENT, and QUEST items are sold at their respective shops.\nThey’re not available yet, so let’s give you some for demonstration.</t>
-  </si>
-  <si>
-    <t>幸运、移动、任务物资在对应的商店出售。\n目前没有地方能买到呢，先发放一些物资以作说明吧。</t>
-  </si>
-  <si>
-    <t>TUTORIAL_POINTS_4</t>
-  </si>
-  <si>
-    <t>Success rate increased!\nThe more items you prepare, the less likely you are to fail.\nIf you fail... you’ll return empty-handed.</t>
-  </si>
-  <si>
-    <t>冒险成功率提升了！\n物资准备越充分，就越能够避免冒险失败的情况。\n如果失败的话...就一无所获了呢。</t>
-  </si>
-  <si>
-    <t>TUTORIAL_POINTS_5</t>
-  </si>
-  <si>
-    <t>You have 60 days in total.\nThe more time you spend stocking up in the city, the less time you’ll have to venture out.\nAdventure scores also decrease as days pass. Keep that in mind.</t>
-  </si>
-  <si>
-    <t>此外，一共有 60 天的时间。\n花费更多时间在城里囤积物资的话，可用于出城冒险的时间则会相应减少。\n能够获得的冒险得分也会随天数降低。请注意。</t>
-  </si>
-  <si>
-    <t>TUTORIAL_POINTS_6</t>
-  </si>
-  <si>
-    <t>The goal is to achieve a higher adventure score.\nSo, improve your efficiency in stocking up.\nRaise your Success Rate while saving more days for the adventure itself!</t>
-  </si>
-  <si>
-    <t>游戏的目标是获取更高的冒险得分。\n因此，提高在城里准备物资的效率。\n在提高冒险成功率的同时，努力留出更多天数用来冒险吧。</t>
-  </si>
-  <si>
-    <t>When you're ready, head to the city gate to end the tutorial and start the game!</t>
-  </si>
-  <si>
-    <t>提升各类点数可以增加冒险成功率。\n不过需要幸运、移动、任务、商店四项点数共同作用，效果才会显著哦。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得了 1 张商店升级券。\n去商店升级格看看吧。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKIP_TUTORIAL</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>跳过教程</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skip Tutorial</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKIP_TUTORIAL_CONFIRM</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Are you sure to skip tutorial?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>确定要跳过教程吗？</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得了 2 个自选水果。\n点击亮着的水果图标，挑选想要的吧。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>手动刷新次数会在每日00:00重置为 3 次。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Please visit the shop again and buy the [font_size=40][color=#94b757]Balance[/color][/font_size].\nIf it isn’t available, try the manual refresh you just unlocked.</t>
-  </si>
-  <si>
-    <t>请再次拜访商店，买下 [font_size=40][color=#94b757]天平[/color][/font_size] 吧。\n如果目前没有上架的话，试试刚解锁的手动刷新吧。</t>
-  </si>
-  <si>
-    <t>The [font_size=40][color=#94b757]天平[/color][/font_size] provides 5 Shop Pts.</t>
-  </si>
-  <si>
-    <t>买到的 [font_size=40][color=#94b757]天平[/color][/font_size] 可以提供 3 点商店点数。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Just [font_size=40]Grapes x 1[/font_size] left to complete the quest.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Try stopping on that strange tile over there.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>“Thanks for the fruit! Here are [font_size=40]Exchange Coupons x 2[/font_size].\nYou can use them at the shop.”</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>“I need [font_size=40]Apple x 1[/font_size] and [font_size=40]Grapes x1[/font_size], please!”</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Another [font_size=40]Quest[/font_size]? Go pay them a visit.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>You got [font_size=40]Fruit of Your Choice x 2[/font_size]!\nClick the glowing fruit icons to pick the ones you want.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>现在还没有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">[font_size=40] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>升级券</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> [/font_size]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>呢。\n先努力获取[font_size=40] 交换券[/font_size]，再去升级格购买吧。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">There are currently two upgrades available.\nHow about buying “Shop Manual Refresh” first?  </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[font_size=40][color=#94b757]天平[/color][/font_size] 可以提供[font_size=40] 3 商店点数[/font_size]。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Raising different types of points increases adventure success rate.\nBut only when all four types work together will the effect be significant.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[font_size=40][color=#94b757]Balance[/color][/font_size] provides [font_size=40]3 Shop Pts[/font_size].</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>It's time to get prepared in the city for the upcoming adventure.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>You got [font_size=40]Apple x 1[/font_size]!\nNot sure what it's for yet...</t>
+  </si>
+  <si>
+    <t>“Thanks for the message! Here's [font_size=40]Exchange Coupon x 1[/font_size].\nCheck out the nearby shop when you can.”</t>
+  </si>
+  <si>
+    <t>The four types of items are sold at their respective shops.\nThey're not available yet, so let's give you some for demonstration.</t>
+  </si>
+  <si>
+    <t>If you [font_size=40]fail[/font_size]... you'll return [color=#BC3D37]empty-handed[/color].</t>
+  </si>
+  <si>
+    <t>Unlike [font_size=40]Accepting Quests[/font_size],\n[font_size=40]Completing Quests[/font_size] doesn't require stopping on the tile. \nPassing through will automatically deliver them.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sometimes you'll also receive [font_size=40]message delivery Quests[/font_size], \nnot just fruit ones.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">At the [font_size=40]Upgrade Tile[/font_size], \nyou can use [font_size=40]Upgrade Coupons[/font_size] to purchase various [font_size=40]Upgrades[/font_size].  </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">You don't have any [font_size=40]Upgrade Coupons[/font_size] yet.\nFirst, try to earn some [font_size=40]Exchange Coupons[/font_size], \nthen head to the tile to buy upgrades.  </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>You obtained [font_size=40]Shop Upgrade Coupon x 1[/font_size].\nGo check the shop upgrade tile.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Every day at [color=#BC3D37]00:00[/color], \nthe shop restocks with random items and also resets your 3 manual refresh uses.  </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Aside from the unlimited Mystery Boxes, \nall other items will be temporarily out of stock after being sold.  </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Some upgrades can be purchased multiple times, \nincreasing both their level and effectiveness.  </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Now, please buy [font_size=40][color=#94b757]Balance[/color] x 1[/font_size] from the shop.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>When you're ready, \nhead to the city gate to end the tutorial and begin your adventure.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -600,6 +902,35 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -782,7 +1113,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -912,6 +1243,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1041,7 +1387,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1049,6 +1395,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1409,548 +1761,544 @@
   <dimension ref="A1:C58"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="36.75" customWidth="1"/>
-    <col min="2" max="2" width="109.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="75.875" customWidth="1"/>
+    <col min="1" max="1" width="23.125" customWidth="1"/>
+    <col min="2" max="2" width="94.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="83.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" t="s">
+      <c r="A2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="4"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="4"/>
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="4"/>
+      <c r="C15" s="4"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="4"/>
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="4"/>
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="28.5">
+      <c r="A23" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="4"/>
+      <c r="C25" s="4"/>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="4"/>
+      <c r="C26" s="4"/>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="4"/>
+      <c r="C27" s="4"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C30" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="28.5">
+      <c r="A31" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="4"/>
+      <c r="C32" s="4"/>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="4"/>
+      <c r="C33" s="4"/>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="4"/>
+      <c r="C37" s="4"/>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="4"/>
+      <c r="C38" s="4"/>
+    </row>
+    <row r="39" spans="1:3" ht="28.5">
+      <c r="A39" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="28.5">
+      <c r="A40" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B40" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="C4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
+      <c r="C40" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="28.5">
+      <c r="A42" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B43" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="B5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2"/>
-      <c r="C13" s="2"/>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2"/>
-      <c r="C14" s="2"/>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2"/>
-      <c r="C15" s="2"/>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2"/>
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="C43" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A44" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A45" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A46" s="4"/>
+      <c r="C46" s="4"/>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="4"/>
+      <c r="C47" s="4"/>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="4"/>
+      <c r="C48" s="4"/>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="4" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2"/>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" t="s">
-        <v>72</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>58</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="2"/>
-      <c r="C26" s="2"/>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="2"/>
-      <c r="C27" s="2"/>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="2"/>
-      <c r="C28" s="2"/>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B29" t="s">
-        <v>76</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B30" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B31" t="s">
-        <v>79</v>
-      </c>
-      <c r="C31" s="2" t="s">
+      <c r="B49" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C49" s="4" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="2" t="s">
+    <row r="50" spans="1:3">
+      <c r="A50" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="28.5">
+      <c r="A51" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C51" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B32" t="s">
+    </row>
+    <row r="52" spans="1:3" ht="28.5">
+      <c r="A52" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C52" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="2" t="s">
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C53" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B33" t="s">
-        <v>60</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="2"/>
-      <c r="C34" s="2"/>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B35" s="2" t="s">
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B37" s="2" t="s">
+      <c r="B55" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="28.5">
+      <c r="A56" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="2"/>
-      <c r="C38" s="2"/>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="2"/>
-      <c r="C39" s="2"/>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B40" s="2" t="s">
+      <c r="B56" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="28.5">
+      <c r="A57" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B43" s="2" t="s">
+      <c r="B57" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C57" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A45" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A46" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A47" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="28.5">
-      <c r="A50" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="28.5">
-      <c r="A52" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="28.5">
-      <c r="A53" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="28.5">
-      <c r="A54" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="28.5">
-      <c r="A55" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="28.5">
-      <c r="A56" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>118</v>
+        <v>32</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>129</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Internationalization/Tutorial_String_Data.xlsx
+++ b/Assets/Internationalization/Tutorial_String_Data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Game Projects\Godot Projects\city_of_circling\Assets\Internationalization\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\city_of_circling\city_of_circling\Assets\Internationalization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E987EC52-A35E-4892-AAC3-2A14A964DFFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76A71328-EA98-4F2C-915D-A068F8CCCD3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{08590711-CB36-410F-B5A8-7B8F5AA8D814}"/>
+    <workbookView xWindow="-38510" yWindow="1250" windowWidth="38620" windowHeight="21100" xr2:uid="{08590711-CB36-410F-B5A8-7B8F5AA8D814}"/>
   </bookViews>
   <sheets>
     <sheet name="String_Data" sheetId="1" r:id="rId1"/>
@@ -146,9 +146,6 @@
     <t>add_grid()</t>
   </si>
   <si>
-    <t>Someone seems to need help.\nGo pay them a visit.</t>
-  </si>
-  <si>
     <t>TUTORIAL_NPC_11</t>
   </si>
   <si>
@@ -269,26 +266,388 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>获得了[font_size=40] 苹果 x 1[/font_size]。\n虽然不知道能用来做什么...</t>
-  </si>
-  <si>
-    <t>似乎有人需要帮助。\n去拜访看看吧。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>还差[font_size=40] 葡萄 x 1[/font_size] 就能完成委托。</t>
-  </si>
-  <si>
     <t>抽到了需要的水果。\n现在回去提交吧。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>“我需要[font_size=40] 苹果 x 1[/font_size] 和[font_size=40] 葡萄 x 1[/font_size]，拜托了！”</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>不同于[font_size=40] 接受任务[/font_size]，\n</t>
+    <t>"可以麻烦帮我传个信给长颈鹿吗？拜托了！”</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得了[font_size=40] 自选水果 x 2[/font_size]。\n点击闪烁的水果图标，挑选想要的吧。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>有些升级项可以反复购买，等级和效果随之提升。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>商店会在</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[color=#BC3D37]每天 00:00 [/color]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>上架随机商品，同时重置3次手动刷新次数。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升各类点数可以增加冒险成功率。\n不过需要四种点数共同作用，效果才会显著哦。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>四类点数道具会在对应的商店出售。\n目前没有商店能买到其他三类呢，先发放一些道具以作说明吧。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>冒险成功率提升了！\n道具准备越充分，就越能够避免冒险失败的情况。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TUTORIAL_POINTS_7</t>
+  </si>
+  <si>
+    <t>TUTORIAL_POINTS_8</t>
+  </si>
+  <si>
+    <t>TUTORIAL_POINTS_9</t>
+  </si>
+  <si>
+    <r>
+      <t>如果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[font_size=40] 失败 [/font_size]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的话...就[color=#BC3D37] 一无所获 [/color]了呢。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>此外，游戏一共有[color=#BC3D37] 60 天[/color]的时间。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>花费更多时间在城里囤积道具的话，可用于出城冒险的时间则会相应减少。\n能够获得的[color=#BC3D37]  冒险得分 [/color]也会随天数降低。请注意。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏的目标是获取更高的[color=#BC3D37]  冒险得分[/color]。\n因此, 在城里囤积道具的同时，努力留出更多时间用来冒险吧。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>You're ready to proceed.</t>
+  </si>
+  <si>
+    <t>Skip Tutorial</t>
+  </si>
+  <si>
+    <t>Welcome to the Tutorial.</t>
+  </si>
+  <si>
+    <t>Move your mouse along the tiles to plan a path,\nthen click the destination to confirm.</t>
+  </si>
+  <si>
+    <t>Are you sure to skip the tutorial?</t>
+  </si>
+  <si>
+    <t>Each move takes [color=#BC3D37]3 hours[/color]. Keep that in mind.</t>
+  </si>
+  <si>
+    <t>“Could you deliver a message to the Giraffe for me? Please!”</t>
+  </si>
+  <si>
+    <t>Other items are a bit pricey for now.\nHow about trying a Mystery Box instead?</t>
+  </si>
+  <si>
+    <t>Adventure success rate increased!\nThe more items you prepare, the less likely you are to fail.</t>
+  </si>
+  <si>
+    <t>Spending more time stocking up in the city means less time left for adventures.\nYour [color=#BC3D37]Adventure Score[/color] will also decrease as days pass. Keep that in mind.</t>
+  </si>
+  <si>
+    <t>The goal is to achieve a higher [color=#BC3D37]Adventure Score[/color].\nSo, stock up efficiently and leave more time for the adventure itself!</t>
+  </si>
+  <si>
+    <t>The game lasts [color=#BC3D37]60 days[/color] in total.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>准备妥当的话，就前往城门结束教程，正式开始游戏吧。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Just [font_size=40]Grapes x 1[/font_size] left to complete the quest.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Try stopping on that strange tile over there.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>“Thanks for the fruit! Here are [font_size=40]Exchange Coupons x 2[/font_size].\nYou can use them at the shop.”</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>“I need [font_size=40]Apple x 1[/font_size] and [font_size=40]Grapes x1[/font_size], please!”</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Another [font_size=40]Quest[/font_size]? Go pay them a visit.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>You got [font_size=40]Fruit of Your Choice x 2[/font_size]!\nClick the glowing fruit icons to pick the ones you want.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">There are currently two upgrades available.\nHow about buying “Shop Manual Refresh” first?  </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Raising different types of points increases adventure success rate.\nBut only when all four types work together will the effect be significant.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[font_size=40][color=#94b757]Balance[/color][/font_size] provides [font_size=40]3 Shop Pts[/font_size].</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>It's time to get prepared in the city for the upcoming adventure.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>You got [font_size=40]Apple x 1[/font_size]!\nNot sure what it's for yet...</t>
+  </si>
+  <si>
+    <t>The four types of items are sold at their respective shops.\nThey're not available yet, so let's give you some for demonstration.</t>
+  </si>
+  <si>
+    <t>If you [font_size=40]fail[/font_size]... you'll return [color=#BC3D37]empty-handed[/color].</t>
+  </si>
+  <si>
+    <t>Unlike [font_size=40]Accepting Quests[/font_size],\n[font_size=40]Completing Quests[/font_size] doesn't require stopping on the tile. \nPassing through will automatically deliver them.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">At the [font_size=40]Upgrade Tile[/font_size], \nyou can use [font_size=40]Upgrade Coupons[/font_size] to purchase various [font_size=40]Upgrades[/font_size].  </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>You obtained [font_size=40]Shop Upgrade Coupon x 1[/font_size].\nGo check the shop upgrade tile.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Every day at [color=#BC3D37]00:00[/color], \nthe shop restocks with random items and also resets your 3 manual refresh uses.  </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Some upgrades can be purchased multiple times, \nincreasing both their level and effectiveness.  </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Now, please buy [font_size=40][color=#94b757]Balance[/color] x 1[/font_size] from the shop.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>When you're ready, \nhead to the city gate to end the tutorial and begin your adventure.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>似乎有人正在发布任务。\n去拜访看看吧。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Seems like someone's posting a quest.\nGo pay them a visit.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">“我需要[font_size=40] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>苹果 x 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">[/font_size] 和[font_size=40] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>葡萄 x 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[/font_size]，拜托了！”</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">还差[font_size=40] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>葡萄 x 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[/font_size] 就能完成任务。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">获得了[font_size=40] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>苹果 x 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[/font_size]。\n虽然不知道能用来做什么...</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">“感谢你的水果！送你[font_size=40] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>交换券 x 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[/font_size]，可以用来在商店购物哦。”</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">不同于[font_size=40] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>接受任务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[/font_size]，\n</t>
     </r>
     <r>
       <rPr>
@@ -338,75 +697,149 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>“感谢你的水果！送你[font_size=40] 交换券 x 2[/font_size]，可以用来在商店购物哦。”</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>另一位似乎也有[font_size=40] 任务[/font_size]？拜访看看吧。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>"可以麻烦帮我传个信给长颈鹿吗？拜托了！”</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>除了水果，有时也会接到传信的[font_size=40] 任务[/font_size]。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>“感谢！给你[font_size=40] 交换券 x 1[/font_size]，有空的话去附近的商店看看吧。”</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>商店开张，可以用交换券购物了。\n进去看看吧。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>其他商品有点贵。\n不如先买个盲盒碰碰运气？</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得了[font_size=40] 自选水果 x 2[/font_size]。\n点击闪烁的水果图标，挑选想要的吧。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>除了无限供应的盲盒，其他商品出售后都会暂时缺货。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>目前有两种升级可选。\n不如先买“解锁商店刷新”？</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>有些升级项可以反复购买，等级和效果随之提升。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>商店会在</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[color=#BC3D37]每天 00:00 [/color]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>上架随机商品，同时重置3次手动刷新次数。</t>
+    <r>
+      <t>除了</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>水果任务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">，有时也会接到[font_size=40] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>传信任务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[/font_size]。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">“感谢！给你[font_size=40] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>交换券</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> x 1[/font_size]，有空的话去附近的商店看看吧。”</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>商店</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>开张，可以用</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>交换券</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>购物了。\n进去看看吧。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>其他商品有点贵。\n不如先买个</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>盲盒</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>碰碰运气？</t>
     </r>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -446,11 +879,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
       <t>升级券</t>
@@ -472,7 +904,26 @@
         <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[font_size=40] 升级[/font_size]</t>
+      <t xml:space="preserve">[font_size=40] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>升级</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[/font_size]</t>
     </r>
     <r>
       <rPr>
@@ -488,135 +939,158 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>获得了[font_size=40] 商店升级券 x 1[/font_size]。\n去商店升级格看看吧。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>现在请从商店获取[font_size=40][color=#94b757] 天平 [/color] x 1 [/font_size]吧。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>提升各类点数可以增加冒险成功率。\n不过需要四种点数共同作用，效果才会显著哦。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>四类点数道具会在对应的商店出售。\n目前没有商店能买到其他三类呢，先发放一些道具以作说明吧。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>冒险成功率提升了！\n道具准备越充分，就越能够避免冒险失败的情况。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>TUTORIAL_POINTS_7</t>
-  </si>
-  <si>
-    <t>TUTORIAL_POINTS_8</t>
-  </si>
-  <si>
-    <t>TUTORIAL_POINTS_9</t>
-  </si>
-  <si>
-    <r>
-      <t>如果</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[font_size=40] 失败 [/font_size]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>的话...就[color=#BC3D37] 一无所获 [/color]了呢。</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>此外，游戏一共有[color=#BC3D37] 60 天[/color]的时间。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>花费更多时间在城里囤积道具的话，可用于出城冒险的时间则会相应减少。\n能够获得的[color=#BC3D37]  冒险得分 [/color]也会随天数降低。请注意。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>游戏的目标是获取更高的[color=#BC3D37]  冒险得分[/color]。\n因此, 在城里囤积道具的同时，努力留出更多时间用来冒险吧。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>You're ready to proceed.</t>
-  </si>
-  <si>
-    <t>Skip Tutorial</t>
-  </si>
-  <si>
-    <t>Welcome to the Tutorial.</t>
-  </si>
-  <si>
-    <t>Move your mouse along the tiles to plan a path,\nthen click the destination to confirm.</t>
-  </si>
-  <si>
-    <t>Are you sure to skip the tutorial?</t>
-  </si>
-  <si>
-    <t>Each move takes [color=#BC3D37]3 hours[/color]. Keep that in mind.</t>
-  </si>
-  <si>
-    <t>“Could you deliver a message to the Giraffe for me? Please!”</t>
-  </si>
-  <si>
-    <t>Other items are a bit pricey for now.\nHow about trying a Mystery Box instead?</t>
-  </si>
-  <si>
-    <t>Adventure success rate increased!\nThe more items you prepare, the less likely you are to fail.</t>
-  </si>
-  <si>
-    <t>Spending more time stocking up in the city means less time left for adventures.\nYour [color=#BC3D37]Adventure Score[/color] will also decrease as days pass. Keep that in mind.</t>
-  </si>
-  <si>
-    <t>The goal is to achieve a higher [color=#BC3D37]Adventure Score[/color].\nSo, stock up efficiently and leave more time for the adventure itself!</t>
-  </si>
-  <si>
-    <t>The game lasts [color=#BC3D37]60 days[/color] in total.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>准备妥当的话，就前往城门结束教程，正式开始游戏吧。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Just [font_size=40]Grapes x 1[/font_size] left to complete the quest.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Try stopping on that strange tile over there.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>“Thanks for the fruit! Here are [font_size=40]Exchange Coupons x 2[/font_size].\nYou can use them at the shop.”</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>“I need [font_size=40]Apple x 1[/font_size] and [font_size=40]Grapes x1[/font_size], please!”</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Another [font_size=40]Quest[/font_size]? Go pay them a visit.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>You got [font_size=40]Fruit of Your Choice x 2[/font_size]!\nClick the glowing fruit icons to pick the ones you want.</t>
+    <r>
+      <t>除了无限供应的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>盲盒</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，其他商品出售后都会暂时缺货。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">获得了[font_size=40] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>商店升级券 x 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[/font_size]。\n去</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>商店升级格</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>看看吧。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>目前有两种升级可选。\n不如先买“</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>解锁商店刷新</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>”？</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">现在请从商店购买[font_size=40][color=#94b757] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>天平</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> [/color] x 1 [/font_size]吧。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">另一位似乎也有[font_size=40] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>任务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[/font_size]？拜访看看吧。</t>
+    </r>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -634,11 +1108,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
       <t>升级券</t>
@@ -661,80 +1134,160 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>呢。\n先努力获取[font_size=40] 交换券[/font_size]，再去升级格购买吧。</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">There are currently two upgrades available.\nHow about buying “Shop Manual Refresh” first?  </t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>[font_size=40][color=#94b757]天平[/color][/font_size] 可以提供[font_size=40] 3 商店点数[/font_size]。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Raising different types of points increases adventure success rate.\nBut only when all four types work together will the effect be significant.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>[font_size=40][color=#94b757]Balance[/color][/font_size] provides [font_size=40]3 Shop Pts[/font_size].</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>It's time to get prepared in the city for the upcoming adventure.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>You got [font_size=40]Apple x 1[/font_size]!\nNot sure what it's for yet...</t>
+      <t xml:space="preserve">呢。\n先努力获取[font_size=40] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>交换券</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[/font_size]，再去</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>商店</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>购买吧。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[font_size=40][color=#94b757]</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>天平</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[/color][/font_size] 可以提供[font_size=40] 3 商店点数[/font_size]。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Sometimes you'll also receive [font_size=40]</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>message delivery Quests</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">[/font_size], \nnot just </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>fruit Quests</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>“Thanks for the message! Here's [font_size=40]Exchange Coupon x 1[/font_size].\nCheck out the nearby shop when you can.”</t>
-  </si>
-  <si>
-    <t>The four types of items are sold at their respective shops.\nThey're not available yet, so let's give you some for demonstration.</t>
-  </si>
-  <si>
-    <t>If you [font_size=40]fail[/font_size]... you'll return [color=#BC3D37]empty-handed[/color].</t>
-  </si>
-  <si>
-    <t>Unlike [font_size=40]Accepting Quests[/font_size],\n[font_size=40]Completing Quests[/font_size] doesn't require stopping on the tile. \nPassing through will automatically deliver them.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sometimes you'll also receive [font_size=40]message delivery Quests[/font_size], \nnot just fruit ones.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">At the [font_size=40]Upgrade Tile[/font_size], \nyou can use [font_size=40]Upgrade Coupons[/font_size] to purchase various [font_size=40]Upgrades[/font_size].  </t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">You don't have any [font_size=40]Upgrade Coupons[/font_size] yet.\nFirst, try to earn some [font_size=40]Exchange Coupons[/font_size], \nthen head to the tile to buy upgrades.  </t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>You obtained [font_size=40]Shop Upgrade Coupon x 1[/font_size].\nGo check the shop upgrade tile.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Every day at [color=#BC3D37]00:00[/color], \nthe shop restocks with random items and also resets your 3 manual refresh uses.  </t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Aside from the unlimited Mystery Boxes, \nall other items will be temporarily out of stock after being sold.  </t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Some upgrades can be purchased multiple times, \nincreasing both their level and effectiveness.  </t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Now, please buy [font_size=40][color=#94b757]Balance[/color] x 1[/font_size] from the shop.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>When you're ready, \nhead to the city gate to end the tutorial and begin your adventure.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">You don't have any [font_size=40]Upgrade Coupons[/font_size] yet.\nGather some [font_size=40]Exchange Coupons[/font_size] first, \nthen visit the shop to buy one.  </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Aside from the unlimited </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mystery Boxes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, \nall o ther items will be temporarily out of stock after being sold.  </t>
+    </r>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1387,7 +1940,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1403,50 +1956,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="标题" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="标题 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="标题 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="标题 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="标题 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="差" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="汇总" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="计算" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="检查单元格" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="解释性文本" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="警告文本" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="链接单元格" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="适中" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="输出" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="输入" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="着色 1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="着色 2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="着色 3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="着色 4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="着色 5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="着色 6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="注释" xfId="15" builtinId="10" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1462,9 +2018,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1502,7 +2058,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1608,7 +2164,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1750,7 +2306,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1759,11 +2315,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2D1D195-E5E8-4810-8E47-E25327235024}">
   <dimension ref="A1:C58"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="23.125" customWidth="1"/>
-    <col min="2" max="2" width="94.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="83.625" customWidth="1"/>
+    <col min="1" max="1" width="23.08203125" customWidth="1"/>
+    <col min="2" max="2" width="94.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="83.58203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1793,7 +2349,7 @@
         <v>25</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>33</v>
@@ -1801,24 +2357,24 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1826,21 +2382,21 @@
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1851,7 +2407,7 @@
         <v>36</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1859,10 +2415,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1870,10 +2426,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1887,10 +2443,10 @@
         <v>7</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1898,10 +2454,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>60</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1925,10 +2481,10 @@
         <v>9</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>61</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1936,10 +2492,10 @@
         <v>10</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>64</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1947,10 +2503,10 @@
         <v>11</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>62</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1972,18 +2528,18 @@
         <v>38</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="28.5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="28">
       <c r="A23" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1991,10 +2547,10 @@
         <v>15</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2014,10 +2570,10 @@
         <v>16</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>67</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -2025,10 +2581,10 @@
         <v>17</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -2036,21 +2592,21 @@
         <v>18</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="28.5">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="28">
       <c r="A31" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>70</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -2066,10 +2622,10 @@
         <v>19</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>71</v>
+        <v>41</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -2077,10 +2633,10 @@
         <v>20</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>72</v>
+        <v>117</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -2088,10 +2644,10 @@
         <v>21</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -2102,26 +2658,26 @@
       <c r="A38" s="4"/>
       <c r="C38" s="4"/>
     </row>
-    <row r="39" spans="1:3" ht="28.5">
+    <row r="39" spans="1:3" ht="28">
       <c r="A39" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="28.5">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="28">
       <c r="A40" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -2129,21 +2685,21 @@
         <v>27</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="28.5">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="28">
       <c r="A42" s="4" t="s">
         <v>28</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -2151,10 +2707,10 @@
         <v>29</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="14.25" customHeight="1">
@@ -2162,10 +2718,10 @@
         <v>30</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="14.25" customHeight="1">
@@ -2173,10 +2729,10 @@
         <v>31</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="14.25" customHeight="1">
@@ -2193,101 +2749,101 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>80</v>
+        <v>122</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="28">
+      <c r="A51" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B50" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="28.5">
-      <c r="A51" s="4" t="s">
+      <c r="B51" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="28">
+      <c r="A52" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B51" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="28.5">
-      <c r="A52" s="4" t="s">
-        <v>46</v>
-      </c>
       <c r="B52" s="4" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="28">
+      <c r="A56" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="28">
+      <c r="A57" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B55" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="28.5">
-      <c r="A56" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="28.5">
-      <c r="A57" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="C57" s="4" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -2295,10 +2851,10 @@
         <v>32</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Internationalization/Tutorial_String_Data.xlsx
+++ b/Assets/Internationalization/Tutorial_String_Data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\city_of_circling\city_of_circling\Assets\Internationalization\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Game Projects\Godot Projects\city_of_circling\Assets\Internationalization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76A71328-EA98-4F2C-915D-A068F8CCCD3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA914C43-ABB2-4E15-A654-59807F139A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="1250" windowWidth="38620" windowHeight="21100" xr2:uid="{08590711-CB36-410F-B5A8-7B8F5AA8D814}"/>
+    <workbookView xWindow="25490" yWindow="-7310" windowWidth="21820" windowHeight="37900" xr2:uid="{08590711-CB36-410F-B5A8-7B8F5AA8D814}"/>
   </bookViews>
   <sheets>
     <sheet name="String_Data" sheetId="1" r:id="rId1"/>
@@ -52,9 +52,6 @@
     <t>TUTORIAL_NPC_1</t>
   </si>
   <si>
-    <t>TUTORIAL_NPC_2</t>
-  </si>
-  <si>
     <t>TUTORIAL_NPC_3</t>
   </si>
   <si>
@@ -497,9 +494,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">“我需要[font_size=40] </t>
-    </r>
-    <r>
       <rPr>
         <b/>
         <sz val="11"/>
@@ -507,7 +501,7 @@
         <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
-      <t>苹果 x 1</t>
+      <t>商店</t>
     </r>
     <r>
       <rPr>
@@ -518,7 +512,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">[/font_size] 和[font_size=40] </t>
+      <t>开张，可以用</t>
     </r>
     <r>
       <rPr>
@@ -528,7 +522,7 @@
         <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
-      <t>葡萄 x 1</t>
+      <t>交换券</t>
     </r>
     <r>
       <rPr>
@@ -539,13 +533,13 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[/font_size]，拜托了！”</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">还差[font_size=40] </t>
+      <t>购物了。\n进去看看吧。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>其他商品有点贵。\n不如先买个</t>
     </r>
     <r>
       <rPr>
@@ -555,7 +549,7 @@
         <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
-      <t>葡萄 x 1</t>
+      <t>盲盒</t>
     </r>
     <r>
       <rPr>
@@ -566,13 +560,13 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[/font_size] 就能完成任务。</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">获得了[font_size=40] </t>
+      <t>碰碰运气？</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>在</t>
     </r>
     <r>
       <rPr>
@@ -582,7 +576,7 @@
         <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
-      <t>苹果 x 1</t>
+      <t>[font_size=40] 升级格 [/font_size]</t>
     </r>
     <r>
       <rPr>
@@ -593,13 +587,16 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[/font_size]。\n虽然不知道能用来做什么...</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">“感谢你的水果！送你[font_size=40] </t>
+      <t>可以用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">[font_size=40] </t>
     </r>
     <r>
       <rPr>
@@ -609,7 +606,45 @@
         <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
-      <t>交换券 x 2</t>
+      <t>升级券</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> [/font_size]购买各种</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">[font_size=40] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>升级</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[/font_size]</t>
     </r>
     <r>
       <rPr>
@@ -620,13 +655,13 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[/font_size]，可以用来在商店购物哦。”</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">不同于[font_size=40] </t>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>除了无限供应的</t>
     </r>
     <r>
       <rPr>
@@ -636,7 +671,7 @@
         <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
-      <t>接受任务</t>
+      <t>盲盒</t>
     </r>
     <r>
       <rPr>
@@ -647,11 +682,26 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[/font_size]，\n</t>
+      <t>，其他商品出售后都会暂时缺货。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">获得了[font_size=40] </t>
     </r>
     <r>
       <rPr>
         <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>商店升级券 x 1</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
@@ -659,7 +709,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[font_size=40]完成</t>
+      <t>[/font_size]。\n去</t>
     </r>
     <r>
       <rPr>
@@ -669,11 +719,10 @@
         <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
-      <t>任务</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
+      <t>商店升级格</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
@@ -681,7 +730,23 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> [/font_size]</t>
+      <t>看看吧。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>目前有两种升级可选。\n不如先买“</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>解锁商店刷新</t>
     </r>
     <r>
       <rPr>
@@ -692,13 +757,13 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>时不需要停留在格子上，路过就会自动交付。</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>除了</t>
+      <t>”？</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">现在请从商店购买[font_size=40][color=#94b757] </t>
     </r>
     <r>
       <rPr>
@@ -708,7 +773,7 @@
         <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
-      <t>水果任务</t>
+      <t>天平</t>
     </r>
     <r>
       <rPr>
@@ -719,17 +784,22 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">，有时也会接到[font_size=40] </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>传信任务</t>
+      <t xml:space="preserve"> [/color] x 1 [/font_size]吧。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">另一位似乎也有[font_size=40] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>任务</t>
     </r>
     <r>
       <rPr>
@@ -740,13 +810,22 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[/font_size]。</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">“感谢！给你[font_size=40] </t>
+      <t>[/font_size]？拜访看看吧。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>现在还没有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">[font_size=40] </t>
     </r>
     <r>
       <rPr>
@@ -756,7 +835,16 @@
         <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
-      <t>交换券</t>
+      <t>升级券</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> [/font_size]</t>
     </r>
     <r>
       <rPr>
@@ -767,11 +855,8 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> x 1[/font_size]，有空的话去附近的商店看看吧。”</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
+      <t xml:space="preserve">呢。\n先努力获取[font_size=40] </t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -780,7 +865,7 @@
         <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
-      <t>商店</t>
+      <t>交换券</t>
     </r>
     <r>
       <rPr>
@@ -791,7 +876,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>开张，可以用</t>
+      <t>[/font_size]，再去</t>
     </r>
     <r>
       <rPr>
@@ -801,7 +886,7 @@
         <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
-      <t>交换券</t>
+      <t>商店</t>
     </r>
     <r>
       <rPr>
@@ -812,13 +897,13 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>购物了。\n进去看看吧。</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>其他商品有点贵。\n不如先买个</t>
+      <t>购买吧。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[font_size=40][color=#94b757]</t>
     </r>
     <r>
       <rPr>
@@ -828,7 +913,7 @@
         <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
-      <t>盲盒</t>
+      <t>天平</t>
     </r>
     <r>
       <rPr>
@@ -839,13 +924,13 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>碰碰运气？</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>在</t>
+      <t>[/color][/font_size] 可以提供[font_size=40] 3 商店点数[/font_size]。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Sometimes you'll also receive [font_size=40]</t>
     </r>
     <r>
       <rPr>
@@ -855,7 +940,7 @@
         <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[font_size=40] 升级格 [/font_size]</t>
+      <t>message delivery Quests</t>
     </r>
     <r>
       <rPr>
@@ -866,16 +951,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>可以用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">[font_size=40] </t>
+      <t xml:space="preserve">[/font_size], \nnot just </t>
     </r>
     <r>
       <rPr>
@@ -885,45 +961,7 @@
         <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
-      <t>升级券</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> [/font_size]购买各种</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">[font_size=40] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>升级</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[/font_size]</t>
+      <t>fruit Quests</t>
     </r>
     <r>
       <rPr>
@@ -934,13 +972,21 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>。</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>除了无限供应的</t>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>“Thanks for the message! Here's [font_size=40]Exchange Coupon x 1[/font_size].\nCheck out the nearby shop when you can.”</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">You don't have any [font_size=40]Upgrade Coupons[/font_size] yet.\nGather some [font_size=40]Exchange Coupons[/font_size] first, \nthen visit the shop to buy one.  </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Aside from the unlimited </t>
     </r>
     <r>
       <rPr>
@@ -950,7 +996,7 @@
         <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
-      <t>盲盒</t>
+      <t>Mystery Boxes</t>
     </r>
     <r>
       <rPr>
@@ -961,23 +1007,30 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>，其他商品出售后都会暂时缺货。</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">获得了[font_size=40] </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>商店升级券 x 1</t>
+      <t xml:space="preserve">, \nall o ther items will be temporarily out of stock after being sold.  </t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得了[img={"height":"60"}]res://Assets/Sprites/Icon/1x/apple.png[/img][font_size=40]苹果 x 1[/font_size]。\n虽然不知道能用来做什么…</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>“我需要[img={"height":"60"}]res://Assets/Sprites/Icon/1x/apple.png[/img][font_size=40]苹果 x 1[/font_size] 和[img={"height":"60"}]res://Assets/Sprites/Icon/1x/grape.png[/img][font_size=40]葡萄 x 1[/font_size]，拜托了！”</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>还差</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[img={"height":"60"}]res://Assets/Sprites/Icon/1x/grape.png[/img]</t>
     </r>
     <r>
       <rPr>
@@ -988,7 +1041,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[/font_size]。\n去</t>
+      <t>[font_size=40]</t>
     </r>
     <r>
       <rPr>
@@ -998,7 +1051,7 @@
         <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
-      <t>商店升级格</t>
+      <t>葡萄 x 1</t>
     </r>
     <r>
       <rPr>
@@ -1009,13 +1062,29 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>看看吧。</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>目前有两种升级可选。\n不如先买“</t>
+      <t>[/font_size] 就能完成任务。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>不同于 [img={"height":"35"}]res://Assets/Sprites/Icon/1x/Quest_new.png[/img] [font_size=40]接受任务[/font_size]，\n [img={"height":"35"}]res://Assets/Sprites/Icon/1x/Quest_complete.png[/img] [font_size=40]完成任务 [/font_size]时不需要停留在格子上，路过就会自动交付。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TUTORIAL_NPC_2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>“感谢你的水果！送你 [img={"height":"50"}]res://Assets/Sprites/Icon/1x/exchange coupon italic.png[/img] [font_size=40]交换券 x 2[/font_size]，可以用来在商店购物哦。”</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>除了 [img={"height":"40"}]res://Assets/Sprites/Icon/1x/Quest_fruit.png[/img] [font_size=40]水果任务[/font_size]，有时也会接到 [img={"height":"50"}]res://Assets/Sprites/Icon/1x/Quest_delivery.png[/img] [font_size=40]传信任务[/font_size]。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>“感谢！给你 [img={"height":"50"}]res://Assets/Sprites/Icon/1x/exchange coupon italic.png[/img] [font_size=40]</t>
     </r>
     <r>
       <rPr>
@@ -1025,7 +1094,7 @@
         <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
-      <t>解锁商店刷新</t>
+      <t>交换券</t>
     </r>
     <r>
       <rPr>
@@ -1036,257 +1105,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>”？</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">现在请从商店购买[font_size=40][color=#94b757] </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>天平</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> [/color] x 1 [/font_size]吧。</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">另一位似乎也有[font_size=40] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>任务</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[/font_size]？拜访看看吧。</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>现在还没有</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">[font_size=40] </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>升级券</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> [/font_size]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">呢。\n先努力获取[font_size=40] </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>交换券</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[/font_size]，再去</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>商店</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>购买吧。</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>[font_size=40][color=#94b757]</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>天平</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[/color][/font_size] 可以提供[font_size=40] 3 商店点数[/font_size]。</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Sometimes you'll also receive [font_size=40]</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>message delivery Quests</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">[/font_size], \nnot just </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>fruit Quests</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>“Thanks for the message! Here's [font_size=40]Exchange Coupon x 1[/font_size].\nCheck out the nearby shop when you can.”</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">You don't have any [font_size=40]Upgrade Coupons[/font_size] yet.\nGather some [font_size=40]Exchange Coupons[/font_size] first, \nthen visit the shop to buy one.  </t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Aside from the unlimited </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Mystery Boxes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, \nall o ther items will be temporarily out of stock after being sold.  </t>
+      <t xml:space="preserve"> x 1[/font_size]，有空的话去附近的商店看看吧。”</t>
     </r>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1961,48 +1780,48 @@
     </xf>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% - 着色 1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="标题" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="标题 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="标题 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="标题 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="标题 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="差" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="汇总" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="计算" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="检查单元格" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="解释性文本" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="警告文本" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="链接单元格" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="适中" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="输出" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="输入" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="着色 1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="着色 2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="着色 3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="着色 4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="着色 5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="着色 6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="注释" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2018,9 +1837,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2058,7 +1877,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2164,7 +1983,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2306,7 +2125,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2315,11 +2134,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2D1D195-E5E8-4810-8E47-E25327235024}">
   <dimension ref="A1:C58"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="23.08203125" customWidth="1"/>
-    <col min="2" max="2" width="94.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="83.58203125" customWidth="1"/>
+    <col min="1" max="1" width="23.125" customWidth="1"/>
+    <col min="2" max="2" width="94.375" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="83.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2335,46 +2154,46 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2382,21 +2201,21 @@
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2404,10 +2223,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2415,10 +2234,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2426,15 +2245,15 @@
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" s="4"/>
     </row>
@@ -2443,21 +2262,21 @@
         <v>7</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="28.5">
       <c r="A13" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2481,76 +2300,76 @@
         <v>9</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="42.75">
       <c r="A19" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="28.5">
+      <c r="A20" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="4" t="s">
-        <v>11</v>
-      </c>
       <c r="B20" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="42.75">
+      <c r="A23" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="28">
-      <c r="A23" s="4" t="s">
+      <c r="B23" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="28.5">
+      <c r="A24" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="B24" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2567,46 +2386,46 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="42.75">
+      <c r="A30" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="B30" s="4" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="28">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="28.5">
       <c r="A31" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -2619,35 +2438,35 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -2658,81 +2477,81 @@
       <c r="A38" s="4"/>
       <c r="C38" s="4"/>
     </row>
-    <row r="39" spans="1:3" ht="28">
+    <row r="39" spans="1:3" ht="28.5">
       <c r="A39" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="28.5">
+      <c r="A40" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="28">
-      <c r="A40" s="4" t="s">
-        <v>23</v>
-      </c>
       <c r="B40" s="4" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="28.5">
+      <c r="A42" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B41" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="28">
-      <c r="A42" s="4" t="s">
-        <v>28</v>
-      </c>
       <c r="B42" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="14.25" customHeight="1">
       <c r="A44" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="14.25" customHeight="1">
       <c r="A45" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="14.25" customHeight="1">
@@ -2749,112 +2568,112 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="28.5">
+      <c r="A51" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B50" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="28">
-      <c r="A51" s="4" t="s">
+      <c r="B51" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="28.5">
+      <c r="A52" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B51" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C51" s="4" t="s">
+      <c r="B52" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C52" s="4" t="s">
         <v>64</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="28">
-      <c r="A52" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="28.5">
+      <c r="A56" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B55" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C55" s="4" t="s">
+      <c r="B56" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C56" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="28">
-      <c r="A56" s="4" t="s">
+    <row r="57" spans="1:3" ht="28.5">
+      <c r="A57" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B57" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C57" s="4" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="28">
-      <c r="A57" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Internationalization/Tutorial_String_Data.xlsx
+++ b/Assets/Internationalization/Tutorial_String_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Game Projects\Godot Projects\city_of_circling\Assets\Internationalization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA914C43-ABB2-4E15-A654-59807F139A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E53A13-337C-412A-AAB8-8A3BAF8092B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25490" yWindow="-7310" windowWidth="21820" windowHeight="37900" xr2:uid="{08590711-CB36-410F-B5A8-7B8F5AA8D814}"/>
   </bookViews>
@@ -146,9 +146,6 @@
     <t>TUTORIAL_NPC_11</t>
   </si>
   <si>
-    <t>The shop is open! You can buy things with Exchange Coupons.\nTake a look.</t>
-  </si>
-  <si>
     <t>TUTORIAL_POINTS_1</t>
   </si>
   <si>
@@ -388,9 +385,6 @@
     <t>“Could you deliver a message to the Giraffe for me? Please!”</t>
   </si>
   <si>
-    <t>Other items are a bit pricey for now.\nHow about trying a Mystery Box instead?</t>
-  </si>
-  <si>
     <t>Adventure success rate increased!\nThe more items you prepare, the less likely you are to fail.</t>
   </si>
   <si>
@@ -400,108 +394,31 @@
     <t>The goal is to achieve a higher [color=#BC3D37]Adventure Score[/color].\nSo, stock up efficiently and leave more time for the adventure itself!</t>
   </si>
   <si>
-    <t>The game lasts [color=#BC3D37]60 days[/color] in total.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>准备妥当的话，就前往城门结束教程，正式开始游戏吧。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Just [font_size=40]Grapes x 1[/font_size] left to complete the quest.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Try stopping on that strange tile over there.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>“Thanks for the fruit! Here are [font_size=40]Exchange Coupons x 2[/font_size].\nYou can use them at the shop.”</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>“I need [font_size=40]Apple x 1[/font_size] and [font_size=40]Grapes x1[/font_size], please!”</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Another [font_size=40]Quest[/font_size]? Go pay them a visit.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>You got [font_size=40]Fruit of Your Choice x 2[/font_size]!\nClick the glowing fruit icons to pick the ones you want.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">There are currently two upgrades available.\nHow about buying “Shop Manual Refresh” first?  </t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Raising different types of points increases adventure success rate.\nBut only when all four types work together will the effect be significant.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>[font_size=40][color=#94b757]Balance[/color][/font_size] provides [font_size=40]3 Shop Pts[/font_size].</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>It's time to get prepared in the city for the upcoming adventure.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>You got [font_size=40]Apple x 1[/font_size]!\nNot sure what it's for yet...</t>
-  </si>
-  <si>
     <t>The four types of items are sold at their respective shops.\nThey're not available yet, so let's give you some for demonstration.</t>
   </si>
   <si>
     <t>If you [font_size=40]fail[/font_size]... you'll return [color=#BC3D37]empty-handed[/color].</t>
   </si>
   <si>
-    <t>Unlike [font_size=40]Accepting Quests[/font_size],\n[font_size=40]Completing Quests[/font_size] doesn't require stopping on the tile. \nPassing through will automatically deliver them.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">At the [font_size=40]Upgrade Tile[/font_size], \nyou can use [font_size=40]Upgrade Coupons[/font_size] to purchase various [font_size=40]Upgrades[/font_size].  </t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>You obtained [font_size=40]Shop Upgrade Coupon x 1[/font_size].\nGo check the shop upgrade tile.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Every day at [color=#BC3D37]00:00[/color], \nthe shop restocks with random items and also resets your 3 manual refresh uses.  </t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Some upgrades can be purchased multiple times, \nincreasing both their level and effectiveness.  </t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Now, please buy [font_size=40][color=#94b757]Balance[/color] x 1[/font_size] from the shop.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>When you're ready, \nhead to the city gate to end the tutorial and begin your adventure.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>似乎有人正在发布任务。\n去拜访看看吧。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Seems like someone's posting a quest.\nGo pay them a visit.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>商店</t>
+    <r>
+      <t xml:space="preserve">另一位似乎也有[font_size=40] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>任务</t>
     </r>
     <r>
       <rPr>
@@ -512,17 +429,30 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>开张，可以用</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>交换券</t>
+      <t>[/font_size]？拜访看看吧。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得了[img={"height":"60"}]res://Assets/Sprites/Icon/1x/apple.png[/img][font_size=40]苹果 x 1[/font_size]。\n虽然不知道能用来做什么…</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>“我需要[img={"height":"60"}]res://Assets/Sprites/Icon/1x/apple.png[/img][font_size=40]苹果 x 1[/font_size] 和[img={"height":"60"}]res://Assets/Sprites/Icon/1x/grape.png[/img][font_size=40]葡萄 x 1[/font_size]，拜托了！”</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>还差</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[img={"height":"60"}]res://Assets/Sprites/Icon/1x/grape.png[/img]</t>
     </r>
     <r>
       <rPr>
@@ -533,13 +463,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>购物了。\n进去看看吧。</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>其他商品有点贵。\n不如先买个</t>
+      <t>[font_size=40]</t>
     </r>
     <r>
       <rPr>
@@ -549,7 +473,7 @@
         <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
-      <t>盲盒</t>
+      <t>葡萄 x 1</t>
     </r>
     <r>
       <rPr>
@@ -560,13 +484,29 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>碰碰运气？</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>在</t>
+      <t>[/font_size] 就能完成任务。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>不同于 [img={"height":"35"}]res://Assets/Sprites/Icon/1x/Quest_new.png[/img] [font_size=40]接受任务[/font_size]，\n [img={"height":"35"}]res://Assets/Sprites/Icon/1x/Quest_complete.png[/img] [font_size=40]完成任务 [/font_size]时不需要停留在格子上，路过就会自动交付。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TUTORIAL_NPC_2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>“感谢你的水果！送你 [img={"height":"50"}]res://Assets/Sprites/Icon/1x/exchange coupon italic.png[/img] [font_size=40]交换券 x 2[/font_size]，可以用来在商店购物哦。”</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>除了 [img={"height":"40"}]res://Assets/Sprites/Icon/1x/Quest_fruit.png[/img] [font_size=40]水果任务[/font_size]，有时也会接到 [img={"height":"50"}]res://Assets/Sprites/Icon/1x/Quest_delivery.png[/img] [font_size=40]传信任务[/font_size]。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>“感谢！给你 [img={"height":"50"}]res://Assets/Sprites/Icon/1x/exchange coupon italic.png[/img] [font_size=40]</t>
     </r>
     <r>
       <rPr>
@@ -576,7 +516,7 @@
         <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[font_size=40] 升级格 [/font_size]</t>
+      <t>交换券</t>
     </r>
     <r>
       <rPr>
@@ -587,16 +527,33 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>可以用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">[font_size=40] </t>
+      <t xml:space="preserve"> x 1[/font_size]，有空的话去附近的商店看看吧。”</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[img={"height":"45"}]res://Assets/Sprites/Icon/1x/trade_shop.png[/img] [font_size=40]商店[/font_size] 开张，可以用 [img={"height":"50"}]res://Assets/Sprites/Icon/1x/exchange coupon italic.png[/img] [font_size=40]交换券 [/font_size]购物了。\n进去看看吧。</t>
+  </si>
+  <si>
+    <t>其他商品有点贵。\n不如先买个[img={"height":"60"}]res://Assets/Sprites/Icon/1x/mystery_box.png[/img][font_size=40]盲盒[/font_size] 碰碰运气？</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>在 [img={"height":"45"}]res://Assets/Sprites/Grid/1x/shop_upgrade.png[/img][font_size=40] 升级格 [/font_size]可以用[img={"height":"60"}]res://Assets/Sprites/Icon/1x/trade upgrade coupon.png[/img][font_size=40]升级券 [/font_size]购买各种[font_size=40] 升级[/font_size]。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>现在还没有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[img={"height":"60"}]res://Assets/Sprites/Icon/1x/trade upgrade coupon.png[/img][font_size=40]</t>
     </r>
     <r>
       <rPr>
@@ -615,36 +572,7 @@
         <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> [/font_size]购买各种</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">[font_size=40] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>升级</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[/font_size]</t>
+      <t xml:space="preserve"> [/font_size]</t>
     </r>
     <r>
       <rPr>
@@ -655,13 +583,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>。</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>除了无限供应的</t>
+      <t>呢。\n先努力获取 [img={"height":"50"}]res://Assets/Sprites/Icon/1x/exchange coupon italic.png[/img] [font_size=40]</t>
     </r>
     <r>
       <rPr>
@@ -671,7 +593,7 @@
         <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
-      <t>盲盒</t>
+      <t>交换券</t>
     </r>
     <r>
       <rPr>
@@ -682,13 +604,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>，其他商品出售后都会暂时缺货。</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">获得了[font_size=40] </t>
+      <t>[/font_size]，再去</t>
     </r>
     <r>
       <rPr>
@@ -698,7 +614,7 @@
         <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
-      <t>商店升级券 x 1</t>
+      <t>商店</t>
     </r>
     <r>
       <rPr>
@@ -709,7 +625,13 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[/font_size]。\n去</t>
+      <t>购买吧。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>除了无限供应的[img={"height":"60"}]res://Assets/Sprites/Icon/1x/mystery_box.png[/img]</t>
     </r>
     <r>
       <rPr>
@@ -719,7 +641,7 @@
         <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
-      <t>商店升级格</t>
+      <t>盲盒</t>
     </r>
     <r>
       <rPr>
@@ -730,23 +652,22 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>看看吧。</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>目前有两种升级可选。\n不如先买“</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>解锁商店刷新</t>
+      <t>，其他商品出售后都会暂时缺货。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>获得了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[img={"height":"60"}]res://Assets/Sprites/Icon/1x/trade upgrade coupon.png[/img]</t>
     </r>
     <r>
       <rPr>
@@ -757,13 +678,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>”？</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">现在请从商店购买[font_size=40][color=#94b757] </t>
+      <t>[font_size=40]</t>
     </r>
     <r>
       <rPr>
@@ -773,7 +688,7 @@
         <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
-      <t>天平</t>
+      <t>商店升级券 x 1</t>
     </r>
     <r>
       <rPr>
@@ -784,22 +699,17 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> [/color] x 1 [/font_size]吧。</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">另一位似乎也有[font_size=40] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>任务</t>
+      <t xml:space="preserve">[/font_size]。\n去 [img={"height":"45"}]res://Assets/Sprites/Grid/1x/shop_upgrade.png[/img] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>商店升级格</t>
     </r>
     <r>
       <rPr>
@@ -810,22 +720,21 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[/font_size]？拜访看看吧。</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>现在还没有</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">[font_size=40] </t>
+      <t>看看吧。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前有两种升级可选。\n不如先买[img={"height":"60"}]res://Assets/Sprites/Icon/1x/shop_manual_refresh.png[/img]“解锁商店刷新”？</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在请再次前往商店购买 [img={"height":"60"}]res://Assets/Sprites/Icon/1x/balance.png[/img][font_size=40][color=#94b757] 天平 [/color] x 1 [/font_size]吧。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[img={"height":"60"}]res://Assets/Sprites/Icon/1x/balance.png[/img] [font_size=40][color=#94b757]</t>
     </r>
     <r>
       <rPr>
@@ -835,16 +744,7 @@
         <rFont val="等线"/>
         <scheme val="minor"/>
       </rPr>
-      <t>升级券</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> [/font_size]</t>
+      <t>天平</t>
     </r>
     <r>
       <rPr>
@@ -855,258 +755,97 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">呢。\n先努力获取[font_size=40] </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>交换券</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[/font_size]，再去</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>商店</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>购买吧。</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>[font_size=40][color=#94b757]</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>天平</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>[/color][/font_size] 可以提供[font_size=40] 3 商店点数[/font_size]。</t>
     </r>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>Sometimes you'll also receive [font_size=40]</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>message delivery Quests</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">[/font_size], \nnot just </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>fruit Quests</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>“Thanks for the message! Here's [font_size=40]Exchange Coupon x 1[/font_size].\nCheck out the nearby shop when you can.”</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">You don't have any [font_size=40]Upgrade Coupons[/font_size] yet.\nGather some [font_size=40]Exchange Coupons[/font_size] first, \nthen visit the shop to buy one.  </t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Aside from the unlimited </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Mystery Boxes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, \nall o ther items will be temporarily out of stock after being sold.  </t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得了[img={"height":"60"}]res://Assets/Sprites/Icon/1x/apple.png[/img][font_size=40]苹果 x 1[/font_size]。\n虽然不知道能用来做什么…</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>“我需要[img={"height":"60"}]res://Assets/Sprites/Icon/1x/apple.png[/img][font_size=40]苹果 x 1[/font_size] 和[img={"height":"60"}]res://Assets/Sprites/Icon/1x/grape.png[/img][font_size=40]葡萄 x 1[/font_size]，拜托了！”</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>还差</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[img={"height":"60"}]res://Assets/Sprites/Icon/1x/grape.png[/img]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[font_size=40]</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>葡萄 x 1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[/font_size] 就能完成任务。</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>不同于 [img={"height":"35"}]res://Assets/Sprites/Icon/1x/Quest_new.png[/img] [font_size=40]接受任务[/font_size]，\n [img={"height":"35"}]res://Assets/Sprites/Icon/1x/Quest_complete.png[/img] [font_size=40]完成任务 [/font_size]时不需要停留在格子上，路过就会自动交付。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>TUTORIAL_NPC_2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>“感谢你的水果！送你 [img={"height":"50"}]res://Assets/Sprites/Icon/1x/exchange coupon italic.png[/img] [font_size=40]交换券 x 2[/font_size]，可以用来在商店购物哦。”</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>除了 [img={"height":"40"}]res://Assets/Sprites/Icon/1x/Quest_fruit.png[/img] [font_size=40]水果任务[/font_size]，有时也会接到 [img={"height":"50"}]res://Assets/Sprites/Icon/1x/Quest_delivery.png[/img] [font_size=40]传信任务[/font_size]。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>“感谢！给你 [img={"height":"50"}]res://Assets/Sprites/Icon/1x/exchange coupon italic.png[/img] [font_size=40]</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>交换券</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> x 1[/font_size]，有空的话去附近的商店看看吧。”</t>
-    </r>
+    <t>It's time to get prepared in the city for the upcoming adventure.</t>
+  </si>
+  <si>
+    <t>Try stopping on that strange tile over there.</t>
+  </si>
+  <si>
+    <t>You got [img={"height":"60"}]res://Assets/Sprites/Icon/1x/apple.png[/img][font_size=40]Apple x 1[/font_size]!\nNot sure what it's for yet...</t>
+  </si>
+  <si>
+    <t>Seems like someone's posting a quest.\nGo pay them a visit.</t>
+  </si>
+  <si>
+    <t>“I need [img={"height":"60"}]res://Assets/Sprites/Icon/1x/apple.png[/img][font_size=40]Apple x 1[/font_size] and [img={"height":"60"}]res://Assets/Sprites/Icon/1x/grape.png[/img][font_size=40]Grapes x 1[/font_size], please!”</t>
+  </si>
+  <si>
+    <t>Just [img={"height":"60"}]res://Assets/Sprites/Icon/1x/grape.png[/img][font_size=40]Grapes x 1[/font_size] left to complete the quest.</t>
+  </si>
+  <si>
+    <t>You got [font_size=40]Fruit of Your Choice x 2[/font_size]!\nClick the glowing fruit icons to pick the ones you want.</t>
+  </si>
+  <si>
+    <t>Aside from the unlimited [img={"height":"60"}]res://Assets/Sprites/Icon/1x/mystery_box.png[/img][font_size=40]Mystery Boxes[/font_size],\nall other items will be temporarily out of stock after being sold.</t>
+  </si>
+  <si>
+    <t>Every day at [color=#BC3D37]00:00[/color],\nthe shop restocks with random items and also resets your 3 manual refresh uses.</t>
+  </si>
+  <si>
+    <t>You obtained [img={"height":"60"}]res://Assets/Sprites/Icon/1x/trade upgrade coupon.png[/img][font_size=40]Shop Upgrade Coupon x 1[/font_size].\nGo check the shop upgrade tile.</t>
+  </si>
+  <si>
+    <t>Some upgrades can be purchased multiple times,\nincreasing both their level and effectiveness.</t>
+  </si>
+  <si>
+    <t>[img={"height":"60"}]res://Assets/Sprites/Icon/1x/balance.png[/img][font_size=40][color=#94b757]Balance[/color][/font_size] provides [font_size=40]3 Shop Pts[/font_size].</t>
+  </si>
+  <si>
+    <t>Raising different types of points increases adventure success rate.\nBut only when all four types work together will the effect be significant.</t>
+  </si>
+  <si>
+    <t>The game lasts [color=#BC3D37]60 days[/color] in total.</t>
+  </si>
+  <si>
+    <t>When you're ready,\nhead to the city gate to end the tutorial and begin your adventure.</t>
+  </si>
+  <si>
+    <t>Unlike [img={"height":"35"}]res://Assets/Sprites/Icon/1x/Quest_new.png[/img] [font_size=40]Accepting Quests[/font_size],\n[img={"height":"35"}]res://Assets/Sprites/Icon/1x/Quest_complete.png[/img] [font_size=40]Completing Quests[/font_size] doesn't require stopping on the tile.\nPassing through will automatically deliver them.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>“Thanks for the fruit! Here are [img={"height":"50"}]res://Assets/Sprites/Icon/1x/exchange coupon italic.png[/img] [font_size=40]Exchange Coupons x 2[/font_size].\nYou can use them at the shop.”</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Another [font_size=40]Quest[/font_size]? Go pay them a visit.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sometimes you'll also receive [img={"height":"40"}]res://Assets/Sprites/Icon/1x/Quest_fruit.png[/img] [font_size=40]Message Delivery Quests[/font_size],\nnot just [img={"height":"50"}]res://Assets/Sprites/Icon/1x/Quest_delivery.png[/img] [font_size=40]Fruit Quests[/font_size].</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>“Thanks for the message! Here's [img={"height":"50"}]res://Assets/Sprites/Icon/1x/exchange coupon italic.png[/img] [font_size=40]Exchange Coupon x 1[/font_size].\nCheck out the nearby shop when you can.”</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Other items are a bit pricey.\nHow about trying a [img={"height":"60"}]res://Assets/Sprites/Icon/1x/mystery_box.png[/img][font_size=40]Mystery Box[/font_size] instead?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>At the [img={"height":"45"}]res://Assets/Sprites/Grid/1x/shop_upgrade.png[/img] [font_size=40]Upgrade Tile[/font_size],\nyou can use [img={"height":"60"}]res://Assets/Sprites/Icon/1x/trade upgrade coupon.png[/img][font_size=40]Upgrade Coupons[/font_size] to purchase various [font_size=40]Upgrades[/font_size].</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>You don't have any [img={"height":"60"}]res://Assets/Sprites/Icon/1x/trade upgrade coupon.png[/img][font_size=40]Upgrade Coupons[/font_size] yet.\nGather some [img={"height":"50"}]res://Assets/Sprites/Icon/1x/exchange coupon italic.png[/img] [font_size=40]Exchange Coupons[/font_size] first,\nthen visit the shop to buy one.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>There are currently two upgrades available.\nHow about buying [img={"height":"60"}]res://Assets/Sprites/Icon/1x/shop_manual_refresh.png[/img][font_size=40]Shop Manual Refresh[/font_size] first?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Now, please buy [img={"height":"60"}]res://Assets/Sprites/Icon/1x/balance.png[/img][font_size=40][color=#94b757]Balance[/color] x 1[/font_size] from the shop.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[img={"height":"45"}]res://Assets/Sprites/Icon/1x/trade_shop.png[/img] [font_size=40]The shop[/font_size] is open!\nYou can buy things with [img={"height":"50"}]res://Assets/Sprites/Icon/1x/exchange coupon italic.png[/img] [font_size=40]Exchange Coupons[/font_size].\nTake a look.</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -2137,18 +1876,18 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="23.125" customWidth="1"/>
-    <col min="2" max="2" width="94.375" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="83.625" customWidth="1"/>
+    <col min="2" max="2" width="90.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="83.625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2156,10 +1895,10 @@
       <c r="A2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2167,88 +1906,88 @@
       <c r="A3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>75</v>
+      <c r="B6" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>95</v>
+        <v>50</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>76</v>
+      <c r="B9" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>78</v>
+      <c r="B10" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2261,22 +2000,22 @@
       <c r="A12" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>87</v>
+      <c r="B12" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="28.5">
       <c r="A13" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>96</v>
+      <c r="B13" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2299,33 +2038,33 @@
       <c r="A18" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="42.75">
       <c r="A19" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="28.5">
       <c r="A20" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>86</v>
+      <c r="B20" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -2347,29 +2086,29 @@
         <v>37</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="42.75">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="57">
       <c r="A23" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>99</v>
+      <c r="B23" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="28.5">
       <c r="A24" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>88</v>
+      <c r="B24" s="1" t="s">
+        <v>120</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2388,44 +2127,44 @@
       <c r="A28" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>90</v>
+      <c r="B28" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>79</v>
+      <c r="B29" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="42.75">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="57">
       <c r="A30" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>118</v>
+      <c r="B30" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="28.5">
       <c r="A31" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>119</v>
+      <c r="B31" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -2436,37 +2175,37 @@
       <c r="A33" s="4"/>
       <c r="C33" s="4"/>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" ht="42.75">
       <c r="A34" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>40</v>
+      <c r="B34" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="42.75">
       <c r="A35" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>80</v>
+      <c r="B35" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="28.5">
       <c r="A36" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -2477,70 +2216,70 @@
       <c r="A38" s="4"/>
       <c r="C38" s="4"/>
     </row>
-    <row r="39" spans="1:3" ht="28.5">
+    <row r="39" spans="1:3" ht="57">
       <c r="A39" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="28.5">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="57">
       <c r="A40" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B40" s="4" t="s">
-        <v>120</v>
+      <c r="B40" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="42.75">
       <c r="A41" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B41" s="4" t="s">
-        <v>121</v>
+      <c r="B41" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="28.5">
       <c r="A42" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B42" s="4" t="s">
-        <v>102</v>
+      <c r="B42" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="42.75">
       <c r="A43" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B43" s="4" t="s">
-        <v>101</v>
+      <c r="B43" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="14.25" customHeight="1">
       <c r="A44" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B44" s="4" t="s">
-        <v>92</v>
+      <c r="B44" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="14.25" customHeight="1">
@@ -2548,10 +2287,10 @@
         <v>30</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="14.25" customHeight="1">
@@ -2566,114 +2305,114 @@
       <c r="A48" s="4"/>
       <c r="C48" s="4"/>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" ht="42.75">
       <c r="A49" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="28.5">
+      <c r="A50" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B49" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>94</v>
+      <c r="B50" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="28.5">
       <c r="A51" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>93</v>
+        <v>42</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="28.5">
       <c r="A52" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>97</v>
+        <v>43</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>98</v>
+        <v>45</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>84</v>
+        <v>65</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="28.5">
       <c r="A56" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>82</v>
+        <v>66</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="28.5">
       <c r="A57" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B58" s="4" t="s">
-        <v>105</v>
+      <c r="B58" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Internationalization/Tutorial_String_Data.xlsx
+++ b/Assets/Internationalization/Tutorial_String_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Game Projects\Godot Projects\city_of_circling\Assets\Internationalization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E53A13-337C-412A-AAB8-8A3BAF8092B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BCBC676-A8AD-4C75-A94D-F0A2D9315FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25490" yWindow="-7310" windowWidth="21820" windowHeight="37900" xr2:uid="{08590711-CB36-410F-B5A8-7B8F5AA8D814}"/>
   </bookViews>
@@ -489,19 +489,11 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>不同于 [img={"height":"35"}]res://Assets/Sprites/Icon/1x/Quest_new.png[/img] [font_size=40]接受任务[/font_size]，\n [img={"height":"35"}]res://Assets/Sprites/Icon/1x/Quest_complete.png[/img] [font_size=40]完成任务 [/font_size]时不需要停留在格子上，路过就会自动交付。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>TUTORIAL_NPC_2</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>“感谢你的水果！送你 [img={"height":"50"}]res://Assets/Sprites/Icon/1x/exchange coupon italic.png[/img] [font_size=40]交换券 x 2[/font_size]，可以用来在商店购物哦。”</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>除了 [img={"height":"40"}]res://Assets/Sprites/Icon/1x/Quest_fruit.png[/img] [font_size=40]水果任务[/font_size]，有时也会接到 [img={"height":"50"}]res://Assets/Sprites/Icon/1x/Quest_delivery.png[/img] [font_size=40]传信任务[/font_size]。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -805,10 +797,6 @@
     <t>When you're ready,\nhead to the city gate to end the tutorial and begin your adventure.</t>
   </si>
   <si>
-    <t>Unlike [img={"height":"35"}]res://Assets/Sprites/Icon/1x/Quest_new.png[/img] [font_size=40]Accepting Quests[/font_size],\n[img={"height":"35"}]res://Assets/Sprites/Icon/1x/Quest_complete.png[/img] [font_size=40]Completing Quests[/font_size] doesn't require stopping on the tile.\nPassing through will automatically deliver them.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>“Thanks for the fruit! Here are [img={"height":"50"}]res://Assets/Sprites/Icon/1x/exchange coupon italic.png[/img] [font_size=40]Exchange Coupons x 2[/font_size].\nYou can use them at the shop.”</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -817,10 +805,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Sometimes you'll also receive [img={"height":"40"}]res://Assets/Sprites/Icon/1x/Quest_fruit.png[/img] [font_size=40]Message Delivery Quests[/font_size],\nnot just [img={"height":"50"}]res://Assets/Sprites/Icon/1x/Quest_delivery.png[/img] [font_size=40]Fruit Quests[/font_size].</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>“Thanks for the message! Here's [img={"height":"50"}]res://Assets/Sprites/Icon/1x/exchange coupon italic.png[/img] [font_size=40]Exchange Coupon x 1[/font_size].\nCheck out the nearby shop when you can.”</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -846,6 +830,22 @@
   </si>
   <si>
     <t>[img={"height":"45"}]res://Assets/Sprites/Icon/1x/trade_shop.png[/img] [font_size=40]The shop[/font_size] is open!\nYou can buy things with [img={"height":"50"}]res://Assets/Sprites/Icon/1x/exchange coupon italic.png[/img] [font_size=40]Exchange Coupons[/font_size].\nTake a look.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>不同于 [img={"height":"35"}]res://Assets/Sprites/Icon/1x/quest_new.png[/img] [font_size=40]接受任务[/font_size]，\n [img={"height":"35"}]res://Assets/Sprites/Icon/1x/quest_complete.png[/img] [font_size=40]完成任务 [/font_size]时不需要停留在格子上，路过就会自动交付。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>除了 [img={"height":"40"}]res://Assets/Sprites/Icon/1x/quest_fruit.png[/img] [font_size=40]水果任务[/font_size]，有时也会接到 [img={"height":"50"}]res://Assets/Sprites/Icon/1x/quest_delivery.png[/img] [font_size=40]传信任务[/font_size]。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sometimes you'll also receive [img={"height":"40"}]res://Assets/Sprites/Icon/1x/quest_fruit.png[/img] [font_size=40]Message Delivery Quests[/font_size],\nnot just [img={"height":"50"}]res://Assets/Sprites/Icon/1x/quest_delivery.png[/img] [font_size=40]Fruit Quests[/font_size].</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unlike [img={"height":"35"}]res://Assets/Sprites/Icon/1x/quest_new.png[/img] [font_size=40]Accepting Quests[/font_size],\n[img={"height":"35"}]res://Assets/Sprites/Icon/1x/quest_complete.png[/img] [font_size=40]Completing Quests[/font_size] doesn't require stopping on the tile.\nPassing through will automatically deliver them.</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1951,7 +1951,7 @@
         <v>50</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>52</v>
@@ -2001,7 +2001,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>56</v>
@@ -2012,7 +2012,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>87</v>
@@ -2039,7 +2039,7 @@
         <v>9</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>85</v>
@@ -2047,10 +2047,10 @@
     </row>
     <row r="19" spans="1:3" ht="42.75">
       <c r="A19" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>88</v>
@@ -2061,7 +2061,7 @@
         <v>10</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>89</v>
@@ -2094,10 +2094,10 @@
         <v>13</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="28.5">
@@ -2105,10 +2105,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2128,7 +2128,7 @@
         <v>15</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>86</v>
@@ -2150,10 +2150,10 @@
         <v>17</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>93</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="28.5">
@@ -2161,10 +2161,10 @@
         <v>39</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -2180,10 +2180,10 @@
         <v>18</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="42.75">
@@ -2191,10 +2191,10 @@
         <v>19</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="28.5">
@@ -2202,7 +2202,7 @@
         <v>20</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>59</v>
@@ -2221,10 +2221,10 @@
         <v>21</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="57">
@@ -2232,10 +2232,10 @@
         <v>22</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="42.75">
@@ -2243,10 +2243,10 @@
         <v>26</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="28.5">
@@ -2254,7 +2254,7 @@
         <v>27</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>61</v>
@@ -2265,10 +2265,10 @@
         <v>28</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="14.25" customHeight="1">
@@ -2276,10 +2276,10 @@
         <v>29</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="14.25" customHeight="1">
@@ -2287,7 +2287,7 @@
         <v>30</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>60</v>
@@ -2310,10 +2310,10 @@
         <v>40</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="28.5">
@@ -2321,10 +2321,10 @@
         <v>41</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="28.5">
@@ -2332,7 +2332,7 @@
         <v>42</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>62</v>
@@ -2376,7 +2376,7 @@
         <v>65</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>69</v>
@@ -2409,7 +2409,7 @@
         <v>31</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>82</v>
